--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -5864,10 +5864,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119710843</v>
+        <v>119710837</v>
       </c>
       <c r="B48" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5876,25 +5876,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5904,10 +5904,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481954</v>
+        <v>481902</v>
       </c>
       <c r="R48" t="n">
-        <v>6781955</v>
+        <v>6781950</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5966,10 +5966,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119710837</v>
+        <v>119710843</v>
       </c>
       <c r="B49" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5978,25 +5978,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6006,10 +6006,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481902</v>
+        <v>481954</v>
       </c>
       <c r="R49" t="n">
-        <v>6781950</v>
+        <v>6781955</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -5018,10 +5018,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119611902</v>
+        <v>119611895</v>
       </c>
       <c r="B40" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5030,25 +5030,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>481962</v>
+        <v>481909</v>
       </c>
       <c r="R40" t="n">
-        <v>6782000</v>
+        <v>6781959</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>10 fkr</t>
+          <t>3fkr</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5232,10 +5232,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119611901</v>
+        <v>119611897</v>
       </c>
       <c r="B42" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5248,21 +5248,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5272,10 +5272,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>481908</v>
+        <v>481923</v>
       </c>
       <c r="R42" t="n">
-        <v>6781965</v>
+        <v>6781922</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5308,11 +5308,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>3fkr</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5339,10 +5334,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119611894</v>
+        <v>119611898</v>
       </c>
       <c r="B43" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5355,21 +5350,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5379,10 +5374,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>481888</v>
+        <v>481943</v>
       </c>
       <c r="R43" t="n">
-        <v>6781967</v>
+        <v>6781924</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5415,6 +5410,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>4fkr</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5441,7 +5441,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119611895</v>
+        <v>119611893</v>
       </c>
       <c r="B44" t="n">
         <v>91884</v>
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>481909</v>
+        <v>481890</v>
       </c>
       <c r="R44" t="n">
-        <v>6781959</v>
+        <v>6781976</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>3fkr</t>
+          <t>10 fkr</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5548,10 +5548,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119611893</v>
+        <v>119611902</v>
       </c>
       <c r="B45" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5560,25 +5560,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5588,10 +5588,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481890</v>
+        <v>481962</v>
       </c>
       <c r="R45" t="n">
-        <v>6781976</v>
+        <v>6782000</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5655,10 +5655,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119611897</v>
+        <v>119611901</v>
       </c>
       <c r="B46" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5671,21 +5671,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5695,10 +5695,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>481923</v>
+        <v>481908</v>
       </c>
       <c r="R46" t="n">
-        <v>6781922</v>
+        <v>6781965</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5731,6 +5731,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>3fkr</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5757,10 +5762,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119611898</v>
+        <v>119611894</v>
       </c>
       <c r="B47" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5773,21 +5778,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5797,10 +5802,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481943</v>
+        <v>481888</v>
       </c>
       <c r="R47" t="n">
-        <v>6781924</v>
+        <v>6781967</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5833,11 +5838,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>4fkr</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5864,10 +5864,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119710837</v>
+        <v>119710843</v>
       </c>
       <c r="B48" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5876,25 +5876,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5904,10 +5904,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481902</v>
+        <v>481954</v>
       </c>
       <c r="R48" t="n">
-        <v>6781950</v>
+        <v>6781955</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5966,10 +5966,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119710843</v>
+        <v>119710837</v>
       </c>
       <c r="B49" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5978,25 +5978,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6006,10 +6006,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481954</v>
+        <v>481902</v>
       </c>
       <c r="R49" t="n">
-        <v>6781955</v>
+        <v>6781950</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -5018,10 +5018,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119611895</v>
+        <v>119611902</v>
       </c>
       <c r="B40" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5030,25 +5030,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>481909</v>
+        <v>481962</v>
       </c>
       <c r="R40" t="n">
-        <v>6781959</v>
+        <v>6782000</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>3fkr</t>
+          <t>10 fkr</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5125,7 +5125,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119611892</v>
+        <v>119611895</v>
       </c>
       <c r="B41" t="n">
         <v>91884</v>
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>481886</v>
+        <v>481909</v>
       </c>
       <c r="R41" t="n">
-        <v>6781973</v>
+        <v>6781959</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>20 fkr</t>
+          <t>3fkr</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5232,7 +5232,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119611897</v>
+        <v>119611893</v>
       </c>
       <c r="B42" t="n">
         <v>91884</v>
@@ -5272,10 +5272,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>481923</v>
+        <v>481890</v>
       </c>
       <c r="R42" t="n">
-        <v>6781922</v>
+        <v>6781976</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5308,6 +5308,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>10 fkr</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5334,10 +5339,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119611898</v>
+        <v>119611894</v>
       </c>
       <c r="B43" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5350,21 +5355,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5374,10 +5379,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>481943</v>
+        <v>481888</v>
       </c>
       <c r="R43" t="n">
-        <v>6781924</v>
+        <v>6781967</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5410,11 +5415,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>4fkr</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5441,7 +5441,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119611893</v>
+        <v>119611897</v>
       </c>
       <c r="B44" t="n">
         <v>91884</v>
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>481890</v>
+        <v>481923</v>
       </c>
       <c r="R44" t="n">
-        <v>6781976</v>
+        <v>6781922</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5517,11 +5517,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>10 fkr</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5548,10 +5543,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119611902</v>
+        <v>119611892</v>
       </c>
       <c r="B45" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5560,25 +5555,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5588,10 +5583,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481962</v>
+        <v>481886</v>
       </c>
       <c r="R45" t="n">
-        <v>6782000</v>
+        <v>6781973</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5628,7 +5623,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>10 fkr</t>
+          <t>20 fkr</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5762,10 +5757,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119611894</v>
+        <v>119611898</v>
       </c>
       <c r="B47" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5778,21 +5773,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5802,10 +5797,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481888</v>
+        <v>481943</v>
       </c>
       <c r="R47" t="n">
-        <v>6781967</v>
+        <v>6781924</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5838,6 +5833,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>4fkr</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -5018,10 +5018,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119611902</v>
+        <v>119611893</v>
       </c>
       <c r="B40" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5030,25 +5030,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>481962</v>
+        <v>481890</v>
       </c>
       <c r="R40" t="n">
-        <v>6782000</v>
+        <v>6781976</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5125,7 +5125,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119611895</v>
+        <v>119611894</v>
       </c>
       <c r="B41" t="n">
         <v>91884</v>
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>481909</v>
+        <v>481888</v>
       </c>
       <c r="R41" t="n">
-        <v>6781959</v>
+        <v>6781967</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5201,11 +5201,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>3fkr</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5232,7 +5227,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119611893</v>
+        <v>119611895</v>
       </c>
       <c r="B42" t="n">
         <v>91884</v>
@@ -5272,10 +5267,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>481890</v>
+        <v>481909</v>
       </c>
       <c r="R42" t="n">
-        <v>6781976</v>
+        <v>6781959</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5312,7 +5307,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>10 fkr</t>
+          <t>3fkr</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5339,7 +5334,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119611894</v>
+        <v>119611892</v>
       </c>
       <c r="B43" t="n">
         <v>91884</v>
@@ -5379,10 +5374,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>481888</v>
+        <v>481886</v>
       </c>
       <c r="R43" t="n">
-        <v>6781967</v>
+        <v>6781973</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5415,6 +5410,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>20 fkr</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5441,10 +5441,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119611897</v>
+        <v>119611898</v>
       </c>
       <c r="B44" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5457,21 +5457,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>481923</v>
+        <v>481943</v>
       </c>
       <c r="R44" t="n">
-        <v>6781922</v>
+        <v>6781924</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5517,6 +5517,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>4fkr</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5543,10 +5548,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119611892</v>
+        <v>119611901</v>
       </c>
       <c r="B45" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5559,21 +5564,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5583,10 +5588,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481886</v>
+        <v>481908</v>
       </c>
       <c r="R45" t="n">
-        <v>6781973</v>
+        <v>6781965</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5623,7 +5628,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>20 fkr</t>
+          <t>3fkr</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5650,10 +5655,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119611901</v>
+        <v>119611897</v>
       </c>
       <c r="B46" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5666,21 +5671,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5690,10 +5695,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>481908</v>
+        <v>481923</v>
       </c>
       <c r="R46" t="n">
-        <v>6781965</v>
+        <v>6781922</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5726,11 +5731,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>3fkr</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5757,10 +5757,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119611898</v>
+        <v>119611902</v>
       </c>
       <c r="B47" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5769,25 +5769,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5797,10 +5797,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481943</v>
+        <v>481962</v>
       </c>
       <c r="R47" t="n">
-        <v>6781924</v>
+        <v>6782000</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5837,7 +5837,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>4fkr</t>
+          <t>10 fkr</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5864,10 +5864,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119710843</v>
+        <v>119710837</v>
       </c>
       <c r="B48" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5876,25 +5876,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5904,10 +5904,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481954</v>
+        <v>481902</v>
       </c>
       <c r="R48" t="n">
-        <v>6781955</v>
+        <v>6781950</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5966,10 +5966,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119710837</v>
+        <v>119710843</v>
       </c>
       <c r="B49" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5978,25 +5978,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6006,10 +6006,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481902</v>
+        <v>481954</v>
       </c>
       <c r="R49" t="n">
-        <v>6781950</v>
+        <v>6781955</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6066,6 +6066,248 @@
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>125153448</v>
+      </c>
+      <c r="B50" t="n">
+        <v>92293</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Unänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>481960</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6782003</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>125153302</v>
+      </c>
+      <c r="B51" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Unänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>481960</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6782003</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -6068,10 +6068,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125153448</v>
+        <v>125153302</v>
       </c>
       <c r="B50" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6080,35 +6080,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6189,10 +6189,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125153302</v>
+        <v>125153448</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6201,35 +6201,35 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -6068,10 +6068,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125153302</v>
+        <v>125153448</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6080,35 +6080,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6189,10 +6189,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125153448</v>
+        <v>125153302</v>
       </c>
       <c r="B51" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6201,35 +6201,35 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -6071,7 +6071,7 @@
         <v>125153448</v>
       </c>
       <c r="B50" t="n">
-        <v>92293</v>
+        <v>92448</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         <v>125153302</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -6068,47 +6068,42 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125153448</v>
+        <v>125153302</v>
       </c>
       <c r="B50" t="n">
-        <v>92448</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6189,47 +6184,42 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125153302</v>
+        <v>125153448</v>
       </c>
       <c r="B51" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92502</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -6187,7 +6187,7 @@
         <v>125153448</v>
       </c>
       <c r="B51" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AY53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6298,6 +6298,220 @@
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>127743814</v>
+      </c>
+      <c r="B52" t="n">
+        <v>92614</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Heden, Heden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>481932</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6781974</v>
+      </c>
+      <c r="S52" t="n">
+        <v>9</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>127743837</v>
+      </c>
+      <c r="B53" t="n">
+        <v>92622</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Heden, Heden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>481926</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6781984</v>
+      </c>
+      <c r="S53" t="n">
+        <v>9</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -6303,7 +6303,7 @@
         <v>127743814</v>
       </c>
       <c r="B52" t="n">
-        <v>92614</v>
+        <v>92620</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>127743837</v>
       </c>
       <c r="B53" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -6303,7 +6303,7 @@
         <v>127743814</v>
       </c>
       <c r="B52" t="n">
-        <v>92620</v>
+        <v>92623</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>127743837</v>
       </c>
       <c r="B53" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -6303,7 +6303,7 @@
         <v>127743814</v>
       </c>
       <c r="B52" t="n">
-        <v>92623</v>
+        <v>92631</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>127743837</v>
       </c>
       <c r="B53" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -6303,7 +6303,7 @@
         <v>127743814</v>
       </c>
       <c r="B52" t="n">
-        <v>92631</v>
+        <v>92632</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>127743837</v>
       </c>
       <c r="B53" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -6303,7 +6303,7 @@
         <v>127743814</v>
       </c>
       <c r="B52" t="n">
-        <v>92634</v>
+        <v>92642</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>127743837</v>
       </c>
       <c r="B53" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AY63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6303,7 +6303,7 @@
         <v>127743814</v>
       </c>
       <c r="B52" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>127743837</v>
       </c>
       <c r="B53" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6511,6 +6511,1130 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128505885</v>
+      </c>
+      <c r="B54" t="n">
+        <v>92734</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Heden, Heden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>481928</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6781979</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128505843</v>
+      </c>
+      <c r="B55" t="n">
+        <v>92778</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Heden, Heden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>481924</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6781967</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128505792</v>
+      </c>
+      <c r="B56" t="n">
+        <v>92742</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Heden, Heden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>481948</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6781929</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128505711</v>
+      </c>
+      <c r="B57" t="n">
+        <v>92742</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Heden, Heden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>481965</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6781946</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128505857</v>
+      </c>
+      <c r="B58" t="n">
+        <v>92778</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Heden, Heden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>481928</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6781979</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128505903</v>
+      </c>
+      <c r="B59" t="n">
+        <v>92767</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>3100</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Talltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Phellodon fuligineoalbus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(J.C.Schmidt) Baird</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Heden, Heden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>481928</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6781979</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128505947</v>
+      </c>
+      <c r="B60" t="n">
+        <v>92770</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Hed, Hed, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>481948</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6782016</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128505610</v>
+      </c>
+      <c r="B61" t="n">
+        <v>90946</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>2051</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Rotfingersvamp</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Ramaria boreimaxima</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Heden, Heden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>481963</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6781979</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128505815</v>
+      </c>
+      <c r="B62" t="n">
+        <v>92730</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>149</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tallgråticka</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Boletopsis grisea</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Peck) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Heden, Heden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>481917</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6781923</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128505701</v>
+      </c>
+      <c r="B63" t="n">
+        <v>90946</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>2051</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Rotfingersvamp</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Ramaria boreimaxima</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Heden, Heden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>481965</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6781946</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AY66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6621,37 +6621,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128505843</v>
+        <v>128505792</v>
       </c>
       <c r="B55" t="n">
-        <v>92778</v>
+        <v>92742</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6665,10 +6665,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481924</v>
+        <v>481948</v>
       </c>
       <c r="R55" t="n">
-        <v>6781967</v>
+        <v>6781929</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6737,37 +6737,37 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128505792</v>
+        <v>128505843</v>
       </c>
       <c r="B56" t="n">
-        <v>92742</v>
+        <v>92778</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6781,10 +6781,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>481948</v>
+        <v>481924</v>
       </c>
       <c r="R56" t="n">
-        <v>6781929</v>
+        <v>6781967</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7636,6 +7636,327 @@
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128619138</v>
+      </c>
+      <c r="B64" t="n">
+        <v>92767</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>3100</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Talltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Phellodon fuligineoalbus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(J.C.Schmidt) Baird</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Heden, Heden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>481932</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6781995</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128619237</v>
+      </c>
+      <c r="B65" t="n">
+        <v>90954</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Hed, Hed, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>481932</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6782005</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>128619059</v>
+      </c>
+      <c r="B66" t="n">
+        <v>92758</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Heden, Heden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>481938</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6781942</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -6517,7 +6517,7 @@
         <v>128505885</v>
       </c>
       <c r="B54" t="n">
-        <v>92734</v>
+        <v>92740</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>128505792</v>
       </c>
       <c r="B55" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>128505843</v>
       </c>
       <c r="B56" t="n">
-        <v>92778</v>
+        <v>92784</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         <v>128505711</v>
       </c>
       <c r="B57" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>128505857</v>
       </c>
       <c r="B58" t="n">
-        <v>92778</v>
+        <v>92784</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         <v>128505903</v>
       </c>
       <c r="B59" t="n">
-        <v>92767</v>
+        <v>92773</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>128505947</v>
       </c>
       <c r="B60" t="n">
-        <v>92770</v>
+        <v>92776</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7302,7 +7302,7 @@
         <v>128505610</v>
       </c>
       <c r="B61" t="n">
-        <v>90946</v>
+        <v>90952</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>128505815</v>
       </c>
       <c r="B62" t="n">
-        <v>92730</v>
+        <v>92736</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>128505701</v>
       </c>
       <c r="B63" t="n">
-        <v>90946</v>
+        <v>90952</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>128619138</v>
       </c>
       <c r="B64" t="n">
-        <v>92767</v>
+        <v>92773</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7748,7 +7748,7 @@
         <v>128619237</v>
       </c>
       <c r="B65" t="n">
-        <v>90954</v>
+        <v>90960</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>128619059</v>
       </c>
       <c r="B66" t="n">
-        <v>92758</v>
+        <v>92764</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -6517,7 +6517,7 @@
         <v>128505885</v>
       </c>
       <c r="B54" t="n">
-        <v>92740</v>
+        <v>92746</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>128505792</v>
       </c>
       <c r="B55" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>128505843</v>
       </c>
       <c r="B56" t="n">
-        <v>92784</v>
+        <v>92790</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         <v>128505711</v>
       </c>
       <c r="B57" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>128505857</v>
       </c>
       <c r="B58" t="n">
-        <v>92784</v>
+        <v>92790</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         <v>128505903</v>
       </c>
       <c r="B59" t="n">
-        <v>92773</v>
+        <v>92779</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>128505947</v>
       </c>
       <c r="B60" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7302,7 +7302,7 @@
         <v>128505610</v>
       </c>
       <c r="B61" t="n">
-        <v>90952</v>
+        <v>90958</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>128505815</v>
       </c>
       <c r="B62" t="n">
-        <v>92736</v>
+        <v>92742</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>128505701</v>
       </c>
       <c r="B63" t="n">
-        <v>90952</v>
+        <v>90958</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>128619138</v>
       </c>
       <c r="B64" t="n">
-        <v>92773</v>
+        <v>92779</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7748,7 +7748,7 @@
         <v>128619237</v>
       </c>
       <c r="B65" t="n">
-        <v>90960</v>
+        <v>90966</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>128619059</v>
       </c>
       <c r="B66" t="n">
-        <v>92764</v>
+        <v>92770</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7957,6 +7957,216 @@
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128712783</v>
+      </c>
+      <c r="B67" t="n">
+        <v>90962</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>5734</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Druvfingersvampar</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Ramaria botrytis s.lat.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Heden, Hed, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>481950</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6782002</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>128712893</v>
+      </c>
+      <c r="B68" t="n">
+        <v>92792</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Hed, Hed, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>481950</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6782002</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -6517,7 +6517,7 @@
         <v>128505885</v>
       </c>
       <c r="B54" t="n">
-        <v>92746</v>
+        <v>92748</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6624,7 +6624,7 @@
         <v>128505792</v>
       </c>
       <c r="B55" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>128505843</v>
       </c>
       <c r="B56" t="n">
-        <v>92790</v>
+        <v>92792</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6856,7 +6856,7 @@
         <v>128505711</v>
       </c>
       <c r="B57" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>128505857</v>
       </c>
       <c r="B58" t="n">
-        <v>92790</v>
+        <v>92792</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7088,7 +7088,7 @@
         <v>128505903</v>
       </c>
       <c r="B59" t="n">
-        <v>92779</v>
+        <v>92781</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7195,7 +7195,7 @@
         <v>128505947</v>
       </c>
       <c r="B60" t="n">
-        <v>92782</v>
+        <v>92784</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
         <v>128505610</v>
       </c>
       <c r="B61" t="n">
-        <v>90958</v>
+        <v>90960</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>128505815</v>
       </c>
       <c r="B62" t="n">
-        <v>92742</v>
+        <v>92744</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>128505701</v>
       </c>
       <c r="B63" t="n">
-        <v>90958</v>
+        <v>90960</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>128619138</v>
       </c>
       <c r="B64" t="n">
-        <v>92779</v>
+        <v>92781</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7748,7 +7748,7 @@
         <v>128619237</v>
       </c>
       <c r="B65" t="n">
-        <v>90966</v>
+        <v>90968</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>128619059</v>
       </c>
       <c r="B66" t="n">
-        <v>92770</v>
+        <v>92772</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6846,7 +6846,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7185,7 +7185,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7952,7 +7952,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -6517,7 +6517,7 @@
         <v>128505885</v>
       </c>
       <c r="B54" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>128505792</v>
       </c>
       <c r="B55" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>128505843</v>
       </c>
       <c r="B56" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         <v>128505711</v>
       </c>
       <c r="B57" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>128505857</v>
       </c>
       <c r="B58" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         <v>128505903</v>
       </c>
       <c r="B59" t="n">
-        <v>92781</v>
+        <v>92782</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>128505947</v>
       </c>
       <c r="B60" t="n">
-        <v>92784</v>
+        <v>92785</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
         <v>128505610</v>
       </c>
       <c r="B61" t="n">
-        <v>90960</v>
+        <v>90961</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>128505815</v>
       </c>
       <c r="B62" t="n">
-        <v>92744</v>
+        <v>92745</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>128505701</v>
       </c>
       <c r="B63" t="n">
-        <v>90960</v>
+        <v>90961</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>128619138</v>
       </c>
       <c r="B64" t="n">
-        <v>92781</v>
+        <v>92782</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7748,7 +7748,7 @@
         <v>128619237</v>
       </c>
       <c r="B65" t="n">
-        <v>90968</v>
+        <v>90969</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>128619059</v>
       </c>
       <c r="B66" t="n">
-        <v>92772</v>
+        <v>92773</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>128712783</v>
       </c>
       <c r="B67" t="n">
-        <v>90962</v>
+        <v>90963</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>128712893</v>
       </c>
       <c r="B68" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -6517,7 +6517,7 @@
         <v>128505885</v>
       </c>
       <c r="B54" t="n">
-        <v>92749</v>
+        <v>92776</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6621,37 +6621,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128505792</v>
+        <v>128505843</v>
       </c>
       <c r="B55" t="n">
-        <v>92757</v>
+        <v>92820</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6665,10 +6665,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481948</v>
+        <v>481924</v>
       </c>
       <c r="R55" t="n">
-        <v>6781929</v>
+        <v>6781967</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6737,37 +6737,37 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128505843</v>
+        <v>128505792</v>
       </c>
       <c r="B56" t="n">
-        <v>92793</v>
+        <v>92784</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6781,10 +6781,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>481924</v>
+        <v>481948</v>
       </c>
       <c r="R56" t="n">
-        <v>6781967</v>
+        <v>6781929</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6856,7 +6856,7 @@
         <v>128505711</v>
       </c>
       <c r="B57" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>128505857</v>
       </c>
       <c r="B58" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         <v>128505903</v>
       </c>
       <c r="B59" t="n">
-        <v>92782</v>
+        <v>92809</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>128505947</v>
       </c>
       <c r="B60" t="n">
-        <v>92785</v>
+        <v>92812</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
         <v>128505610</v>
       </c>
       <c r="B61" t="n">
-        <v>90961</v>
+        <v>90988</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>128505815</v>
       </c>
       <c r="B62" t="n">
-        <v>92745</v>
+        <v>92772</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>128505701</v>
       </c>
       <c r="B63" t="n">
-        <v>90961</v>
+        <v>90988</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>128619138</v>
       </c>
       <c r="B64" t="n">
-        <v>92782</v>
+        <v>92809</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>128619237</v>
       </c>
       <c r="B65" t="n">
-        <v>90969</v>
+        <v>90996</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>128619059</v>
       </c>
       <c r="B66" t="n">
-        <v>92773</v>
+        <v>92800</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>128712783</v>
       </c>
       <c r="B67" t="n">
-        <v>90963</v>
+        <v>90990</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>128712893</v>
       </c>
       <c r="B68" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -6621,37 +6621,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128505843</v>
+        <v>128505792</v>
       </c>
       <c r="B55" t="n">
-        <v>92820</v>
+        <v>92784</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6665,10 +6665,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481924</v>
+        <v>481948</v>
       </c>
       <c r="R55" t="n">
-        <v>6781967</v>
+        <v>6781929</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6737,37 +6737,37 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128505792</v>
+        <v>128505843</v>
       </c>
       <c r="B56" t="n">
-        <v>92784</v>
+        <v>92820</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6781,10 +6781,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>481948</v>
+        <v>481924</v>
       </c>
       <c r="R56" t="n">
-        <v>6781929</v>
+        <v>6781967</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -6517,7 +6517,7 @@
         <v>128505885</v>
       </c>
       <c r="B54" t="n">
-        <v>92776</v>
+        <v>92781</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>128505792</v>
       </c>
       <c r="B55" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>128505843</v>
       </c>
       <c r="B56" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         <v>128505711</v>
       </c>
       <c r="B57" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>128505857</v>
       </c>
       <c r="B58" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         <v>128505903</v>
       </c>
       <c r="B59" t="n">
-        <v>92809</v>
+        <v>92814</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>128505947</v>
       </c>
       <c r="B60" t="n">
-        <v>92812</v>
+        <v>92817</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
         <v>128505610</v>
       </c>
       <c r="B61" t="n">
-        <v>90988</v>
+        <v>90993</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>128505815</v>
       </c>
       <c r="B62" t="n">
-        <v>92772</v>
+        <v>92777</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>128505701</v>
       </c>
       <c r="B63" t="n">
-        <v>90988</v>
+        <v>90993</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>128619138</v>
       </c>
       <c r="B64" t="n">
-        <v>92809</v>
+        <v>92814</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>128619237</v>
       </c>
       <c r="B65" t="n">
-        <v>90996</v>
+        <v>91001</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>128619059</v>
       </c>
       <c r="B66" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>128712783</v>
       </c>
       <c r="B67" t="n">
-        <v>90990</v>
+        <v>90995</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8065,7 +8065,7 @@
         <v>128712893</v>
       </c>
       <c r="B68" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -6517,7 +6517,7 @@
         <v>128505885</v>
       </c>
       <c r="B54" t="n">
-        <v>92781</v>
+        <v>92786</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6621,37 +6621,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128505792</v>
+        <v>128505843</v>
       </c>
       <c r="B55" t="n">
-        <v>92789</v>
+        <v>92832</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6665,10 +6665,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481948</v>
+        <v>481924</v>
       </c>
       <c r="R55" t="n">
-        <v>6781929</v>
+        <v>6781967</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6737,37 +6737,37 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128505843</v>
+        <v>128505792</v>
       </c>
       <c r="B56" t="n">
-        <v>92825</v>
+        <v>92794</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6781,10 +6781,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>481924</v>
+        <v>481948</v>
       </c>
       <c r="R56" t="n">
-        <v>6781967</v>
+        <v>6781929</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6856,7 +6856,7 @@
         <v>128505711</v>
       </c>
       <c r="B57" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>128505857</v>
       </c>
       <c r="B58" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         <v>128505903</v>
       </c>
       <c r="B59" t="n">
-        <v>92814</v>
+        <v>92819</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>128505947</v>
       </c>
       <c r="B60" t="n">
-        <v>92817</v>
+        <v>92823</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7205,21 +7205,12 @@
       <c r="E60" t="n">
         <v>5449</v>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7302,7 +7293,7 @@
         <v>128505610</v>
       </c>
       <c r="B61" t="n">
-        <v>90993</v>
+        <v>90998</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7409,7 +7400,7 @@
         <v>128505815</v>
       </c>
       <c r="B62" t="n">
-        <v>92777</v>
+        <v>92782</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7525,7 +7516,7 @@
         <v>128505701</v>
       </c>
       <c r="B63" t="n">
-        <v>90993</v>
+        <v>90998</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7641,7 +7632,7 @@
         <v>128619138</v>
       </c>
       <c r="B64" t="n">
-        <v>92814</v>
+        <v>92819</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7748,7 +7739,7 @@
         <v>128619237</v>
       </c>
       <c r="B65" t="n">
-        <v>91001</v>
+        <v>91006</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7855,7 +7846,7 @@
         <v>128619059</v>
       </c>
       <c r="B66" t="n">
-        <v>92805</v>
+        <v>92810</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7962,7 +7953,7 @@
         <v>128712783</v>
       </c>
       <c r="B67" t="n">
-        <v>90995</v>
+        <v>91000</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8065,7 +8056,7 @@
         <v>128712893</v>
       </c>
       <c r="B68" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -6621,37 +6621,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128505843</v>
+        <v>128505792</v>
       </c>
       <c r="B55" t="n">
-        <v>92832</v>
+        <v>92794</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6665,10 +6665,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481924</v>
+        <v>481948</v>
       </c>
       <c r="R55" t="n">
-        <v>6781967</v>
+        <v>6781929</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6737,37 +6737,37 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128505792</v>
+        <v>128505843</v>
       </c>
       <c r="B56" t="n">
-        <v>92794</v>
+        <v>92832</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6781,10 +6781,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>481948</v>
+        <v>481924</v>
       </c>
       <c r="R56" t="n">
-        <v>6781929</v>
+        <v>6781967</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -6517,7 +6517,7 @@
         <v>128505885</v>
       </c>
       <c r="B54" t="n">
-        <v>92786</v>
+        <v>92790</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>128505792</v>
       </c>
       <c r="B55" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>128505843</v>
       </c>
       <c r="B56" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         <v>128505711</v>
       </c>
       <c r="B57" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>128505857</v>
       </c>
       <c r="B58" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         <v>128505903</v>
       </c>
       <c r="B59" t="n">
-        <v>92819</v>
+        <v>92823</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>128505947</v>
       </c>
       <c r="B60" t="n">
-        <v>92823</v>
+        <v>92827</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>128505610</v>
       </c>
       <c r="B61" t="n">
-        <v>90998</v>
+        <v>91002</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>128505815</v>
       </c>
       <c r="B62" t="n">
-        <v>92782</v>
+        <v>92786</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7516,7 +7516,7 @@
         <v>128505701</v>
       </c>
       <c r="B63" t="n">
-        <v>90998</v>
+        <v>91002</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>128619138</v>
       </c>
       <c r="B64" t="n">
-        <v>92819</v>
+        <v>92823</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>128619237</v>
       </c>
       <c r="B65" t="n">
-        <v>91006</v>
+        <v>91010</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>128619059</v>
       </c>
       <c r="B66" t="n">
-        <v>92810</v>
+        <v>92814</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>128712783</v>
       </c>
       <c r="B67" t="n">
-        <v>91000</v>
+        <v>91004</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>128712893</v>
       </c>
       <c r="B68" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -7729,7 +7729,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -7729,7 +7729,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -6517,7 +6517,7 @@
         <v>128505885</v>
       </c>
       <c r="B54" t="n">
-        <v>92790</v>
+        <v>92795</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>128505792</v>
       </c>
       <c r="B55" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>128505843</v>
       </c>
       <c r="B56" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         <v>128505711</v>
       </c>
       <c r="B57" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>128505857</v>
       </c>
       <c r="B58" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         <v>128505903</v>
       </c>
       <c r="B59" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>128505947</v>
       </c>
       <c r="B60" t="n">
-        <v>92827</v>
+        <v>92832</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>128505610</v>
       </c>
       <c r="B61" t="n">
-        <v>91002</v>
+        <v>91007</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>128505815</v>
       </c>
       <c r="B62" t="n">
-        <v>92786</v>
+        <v>92791</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7516,7 +7516,7 @@
         <v>128505701</v>
       </c>
       <c r="B63" t="n">
-        <v>91002</v>
+        <v>91007</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>128619138</v>
       </c>
       <c r="B64" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>128619237</v>
       </c>
       <c r="B65" t="n">
-        <v>91010</v>
+        <v>91015</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>128619059</v>
       </c>
       <c r="B66" t="n">
-        <v>92814</v>
+        <v>92819</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>128712783</v>
       </c>
       <c r="B67" t="n">
-        <v>91004</v>
+        <v>91009</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>128712893</v>
       </c>
       <c r="B68" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -6517,7 +6517,7 @@
         <v>128505885</v>
       </c>
       <c r="B54" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6621,37 +6621,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128505792</v>
+        <v>128505843</v>
       </c>
       <c r="B55" t="n">
-        <v>92806</v>
+        <v>92849</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6665,10 +6665,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481948</v>
+        <v>481924</v>
       </c>
       <c r="R55" t="n">
-        <v>6781929</v>
+        <v>6781967</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6737,37 +6737,37 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128505843</v>
+        <v>128505792</v>
       </c>
       <c r="B56" t="n">
-        <v>92844</v>
+        <v>92811</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6781,10 +6781,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>481924</v>
+        <v>481948</v>
       </c>
       <c r="R56" t="n">
-        <v>6781967</v>
+        <v>6781929</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6856,7 +6856,7 @@
         <v>128505711</v>
       </c>
       <c r="B57" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>128505857</v>
       </c>
       <c r="B58" t="n">
-        <v>92844</v>
+        <v>92849</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         <v>128505903</v>
       </c>
       <c r="B59" t="n">
-        <v>92831</v>
+        <v>92836</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>128505947</v>
       </c>
       <c r="B60" t="n">
-        <v>92835</v>
+        <v>92840</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>128505610</v>
       </c>
       <c r="B61" t="n">
-        <v>91009</v>
+        <v>91014</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>128505815</v>
       </c>
       <c r="B62" t="n">
-        <v>92794</v>
+        <v>92799</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7516,7 +7516,7 @@
         <v>128505701</v>
       </c>
       <c r="B63" t="n">
-        <v>91009</v>
+        <v>91014</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>128619138</v>
       </c>
       <c r="B64" t="n">
-        <v>92831</v>
+        <v>92836</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7739,7 +7739,7 @@
         <v>128619237</v>
       </c>
       <c r="B65" t="n">
-        <v>91017</v>
+        <v>91022</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7846,7 +7846,7 @@
         <v>128619059</v>
       </c>
       <c r="B66" t="n">
-        <v>92822</v>
+        <v>92827</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -7953,7 +7953,7 @@
         <v>128712783</v>
       </c>
       <c r="B67" t="n">
-        <v>91016</v>
+        <v>91019</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>128712893</v>
       </c>
       <c r="B68" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -7632,7 +7632,7 @@
         <v>128619138</v>
       </c>
       <c r="B64" t="n">
-        <v>92836</v>
+        <v>92844</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>128619237</v>
       </c>
       <c r="B65" t="n">
-        <v>91022</v>
+        <v>91028</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>128619059</v>
       </c>
       <c r="B66" t="n">
-        <v>92827</v>
+        <v>92835</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>128712783</v>
       </c>
       <c r="B67" t="n">
-        <v>91019</v>
+        <v>91022</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>128712893</v>
       </c>
       <c r="B68" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -7953,7 +7953,7 @@
         <v>128712783</v>
       </c>
       <c r="B67" t="n">
-        <v>91022</v>
+        <v>91026</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>128712893</v>
       </c>
       <c r="B68" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -7953,7 +7953,7 @@
         <v>128712783</v>
       </c>
       <c r="B67" t="n">
-        <v>91026</v>
+        <v>91035</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>128712893</v>
       </c>
       <c r="B68" t="n">
-        <v>92864</v>
+        <v>92873</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67602592</v>
+        <v>119382189</v>
       </c>
       <c r="B2" t="n">
-        <v>88901</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2051</v>
+        <v>149</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -718,20 +713,19 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bjus, 1 km NNO Ribbygget, Dlr</t>
+          <t>Norr Heden, Norr Heden, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481970.0572557269</v>
+        <v>481915</v>
       </c>
       <c r="R2" t="n">
-        <v>6782000.940620476</v>
+        <v>6781923</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-09-14</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-09-14</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,81 +773,50 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>ås med äldre tall</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104286582</v>
+        <v>128505815</v>
       </c>
       <c r="B3" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>149</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -866,21 +829,19 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>N Heden, Dlr</t>
+          <t>Heden, Heden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481926.7278993861</v>
+        <v>481917</v>
       </c>
       <c r="R3" t="n">
-        <v>6781938.439594502</v>
+        <v>6781923</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -904,22 +865,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,61 +889,55 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104286688</v>
+        <v>67602592</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>2051</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -991,20 +946,19 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>N Heden, Dlr</t>
+          <t>Bjus, 1 km NNO Ribbygget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481961.2874401502</v>
+        <v>481970</v>
       </c>
       <c r="R4" t="n">
-        <v>6781986.99354104</v>
+        <v>6782001</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1028,22 +982,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,57 +1000,77 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>ås med äldre tall</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104286577</v>
+        <v>112073185</v>
       </c>
       <c r="B5" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2059</v>
+        <v>2051</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1118,17 +1082,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>N Heden, Dlr</t>
+          <t>Unänget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481926.7278993861</v>
+        <v>481940</v>
       </c>
       <c r="R5" t="n">
-        <v>6781938.439594502</v>
+        <v>6782037</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1152,22 +1116,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1180,62 +1134,82 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>ås</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119039946</v>
+        <v>119039859</v>
       </c>
       <c r="B6" t="n">
-        <v>91822</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>2051</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1246,10 +1220,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481970</v>
+        <v>481974</v>
       </c>
       <c r="R6" t="n">
-        <v>6781999</v>
+        <v>6781922</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1309,15 +1283,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119039859</v>
+        <v>119039877</v>
       </c>
       <c r="B7" t="n">
-        <v>90039</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91394</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,10 +1329,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481974</v>
+        <v>481926</v>
       </c>
       <c r="R7" t="n">
-        <v>6781922</v>
+        <v>6781971</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1423,41 +1392,44 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119039963</v>
+        <v>119039899</v>
       </c>
       <c r="B8" t="n">
-        <v>79142</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91394</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>2051</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1466,10 +1438,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481902</v>
+        <v>481970</v>
       </c>
       <c r="R8" t="n">
-        <v>6781960</v>
+        <v>6781999</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1529,62 +1501,51 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119039990</v>
+        <v>119168967</v>
       </c>
       <c r="B9" t="n">
-        <v>8430</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91394</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>2051</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Unänget, Dlr</t>
+          <t>Heden, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481947</v>
+        <v>481930</v>
       </c>
       <c r="R9" t="n">
-        <v>6781935</v>
+        <v>6781990</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1608,12 +1569,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,27 +1590,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119039877</v>
+        <v>119169080</v>
       </c>
       <c r="B10" t="n">
-        <v>90039</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91394</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,31 +1630,23 @@
           <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Unänget, Dlr</t>
+          <t>Heden, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481926</v>
+        <v>481977</v>
       </c>
       <c r="R10" t="n">
-        <v>6781971</v>
+        <v>6781965</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1722,12 +1670,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1743,59 +1691,49 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119169048</v>
+        <v>119169083</v>
       </c>
       <c r="B11" t="n">
-        <v>57324</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91394</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>2051</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1803,10 +1741,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481942</v>
+        <v>481984</v>
       </c>
       <c r="R11" t="n">
-        <v>6781931</v>
+        <v>6781944</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1847,6 +1785,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1865,56 +1804,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119168985</v>
+        <v>119382026</v>
       </c>
       <c r="B12" t="n">
-        <v>91838</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91394</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>2051</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Heden, Dlr</t>
+          <t>Norr Heden, Norr Heden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481933</v>
+        <v>481916</v>
       </c>
       <c r="R12" t="n">
-        <v>6781977</v>
+        <v>6781966</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1938,12 +1869,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,34 +1893,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119168967</v>
+        <v>128505610</v>
       </c>
       <c r="B13" t="n">
-        <v>90055</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91394</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2005,22 +1940,19 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Heden, Dlr</t>
+          <t>Heden, Heden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481930</v>
+        <v>481963</v>
       </c>
       <c r="R13" t="n">
-        <v>6781990</v>
+        <v>6781979</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2044,12 +1976,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2058,7 +2000,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2070,67 +2011,64 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119169099</v>
+        <v>128505701</v>
       </c>
       <c r="B14" t="n">
-        <v>91838</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91394</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>2051</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Heden, Dlr</t>
+          <t>Heden, Heden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481951</v>
+        <v>481965</v>
       </c>
       <c r="R14" t="n">
-        <v>6781976</v>
+        <v>6781946</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2154,12 +2092,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,7 +2116,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2180,67 +2127,66 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119168971</v>
+        <v>104286577</v>
       </c>
       <c r="B15" t="n">
-        <v>91830</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Heden, Dlr</t>
+          <t>N Heden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
         <v>481927</v>
       </c>
       <c r="R15" t="n">
-        <v>6781985</v>
+        <v>6781938</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2264,12 +2210,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2022-10-23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2022-10-23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,68 +2231,69 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119168889</v>
+        <v>119382046</v>
       </c>
       <c r="B16" t="n">
-        <v>90065</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>256703</v>
+        <v>2059</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Heden, Dlr</t>
+          <t>Norr Heden, Norr Heden, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481930</v>
+        <v>481916</v>
       </c>
       <c r="R16" t="n">
-        <v>6782015</v>
+        <v>6781966</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2370,12 +2317,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2384,76 +2341,66 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119168998</v>
+        <v>119611898</v>
       </c>
       <c r="B17" t="n">
-        <v>98555</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222309</v>
+        <v>2059</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Heden, Dlr</t>
+          <t>Jäsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481913</v>
+        <v>481943</v>
       </c>
       <c r="R17" t="n">
-        <v>6781940</v>
+        <v>6781924</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2477,12 +2424,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>4fkr</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2491,72 +2443,63 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119168914</v>
+        <v>128619059</v>
       </c>
       <c r="B18" t="n">
-        <v>91838</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Heden, Dlr</t>
+          <t>Heden, Heden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481934</v>
+        <v>481938</v>
       </c>
       <c r="R18" t="n">
-        <v>6782015</v>
+        <v>6781942</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2583,12 +2526,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2597,7 +2550,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2609,22 +2561,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119168904</v>
+        <v>128505903</v>
       </c>
       <c r="B19" t="n">
-        <v>91830</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,40 +2579,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Heden, Dlr</t>
+          <t>Heden, Heden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481935</v>
+        <v>481928</v>
       </c>
       <c r="R19" t="n">
-        <v>6782015</v>
+        <v>6781979</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2689,12 +2633,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2703,7 +2657,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2715,67 +2668,55 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119169125</v>
+        <v>128619138</v>
       </c>
       <c r="B20" t="n">
-        <v>91838</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(J.C.Schmidt) Baird</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Heden, Dlr</t>
+          <t>Heden, Heden, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481948</v>
+        <v>481932</v>
       </c>
       <c r="R20" t="n">
-        <v>6781969</v>
+        <v>6781995</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2799,12 +2740,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2813,7 +2764,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2825,69 +2775,66 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119169051</v>
+        <v>112074852</v>
       </c>
       <c r="B21" t="n">
-        <v>8430</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Heden, Dlr</t>
+          <t>Norr Heden, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481942</v>
+        <v>481940</v>
       </c>
       <c r="R21" t="n">
-        <v>6781931</v>
+        <v>6782037</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2911,12 +2858,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2932,49 +2879,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119169080</v>
+        <v>119168904</v>
       </c>
       <c r="B22" t="n">
-        <v>90055</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2051</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2987,13 +2929,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481977</v>
+        <v>481935</v>
       </c>
       <c r="R22" t="n">
-        <v>6781965</v>
+        <v>6782015</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3050,15 +2992,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119169019</v>
+        <v>119168950</v>
       </c>
       <c r="B23" t="n">
-        <v>98555</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3066,27 +3003,30 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222309</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3094,10 +3034,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481920</v>
+        <v>481942</v>
       </c>
       <c r="R23" t="n">
-        <v>6781968</v>
+        <v>6782014</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3157,15 +3097,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119168950</v>
+        <v>119168971</v>
       </c>
       <c r="B24" t="n">
-        <v>91830</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3192,7 +3127,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -3204,10 +3139,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481942</v>
+        <v>481927</v>
       </c>
       <c r="R24" t="n">
-        <v>6782014</v>
+        <v>6781985</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3267,37 +3202,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119168990</v>
+        <v>119168977</v>
       </c>
       <c r="B25" t="n">
-        <v>91838</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3310,10 +3240,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481934</v>
+        <v>481983</v>
       </c>
       <c r="R25" t="n">
-        <v>6781978</v>
+        <v>6781927</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3373,15 +3303,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119169013</v>
+        <v>119382028</v>
       </c>
       <c r="B26" t="n">
-        <v>98555</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3389,38 +3314,43 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222309</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Heden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481920</v>
+        <v>481933</v>
       </c>
       <c r="R26" t="n">
-        <v>6781960</v>
+        <v>6781977</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3447,12 +3377,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3461,7 +3401,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3473,22 +3412,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Bo karlstens, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119168995</v>
+        <v>119382056</v>
       </c>
       <c r="B27" t="n">
-        <v>98555</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3496,41 +3430,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222309</v>
+        <v>4361</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Heden, Dlr</t>
+          <t>Norr Heden, Norr Heden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481914</v>
+        <v>481918</v>
       </c>
       <c r="R27" t="n">
-        <v>6781934</v>
+        <v>6781971</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3554,12 +3493,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3568,80 +3517,72 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119039899</v>
+        <v>119382060</v>
       </c>
       <c r="B28" t="n">
-        <v>90057</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2051</v>
+        <v>4361</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Unänget, Dlr</t>
+          <t>Heden, Heden, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481970</v>
+        <v>481925</v>
       </c>
       <c r="R28" t="n">
-        <v>6781999</v>
+        <v>6781974</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3668,12 +3609,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3682,34 +3633,28 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer, Bo karlstens, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119382060</v>
+        <v>119559723</v>
       </c>
       <c r="B29" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3736,7 +3681,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3746,17 +3691,17 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Heden, Heden, Dlr</t>
+          <t>Norr Heden, Norr Heden, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481925</v>
+        <v>481940</v>
       </c>
       <c r="R29" t="n">
-        <v>6781974</v>
+        <v>6782025</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3780,22 +3725,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3810,27 +3755,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Bo karlstens, Birgitta Kvist</t>
+          <t>Bo karlstens, Anna-Britt Olsson, Erik Danielsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119382046</v>
+        <v>119611901</v>
       </c>
       <c r="B30" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3838,46 +3778,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Norr Heden, Norr Heden, Dlr</t>
+          <t>Jäsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481916</v>
+        <v>481908</v>
       </c>
       <c r="R30" t="n">
-        <v>6781966</v>
+        <v>6781965</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3901,22 +3832,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>09:36</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>09:36</t>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>3fkr</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3936,22 +3862,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119382238</v>
+        <v>119710835</v>
       </c>
       <c r="B31" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3959,26 +3880,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3986,19 +3907,21 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Norr Heden, Norr Heden, Dlr</t>
+          <t>Jäsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481941</v>
+        <v>481902</v>
       </c>
       <c r="R31" t="n">
-        <v>6781954</v>
+        <v>6781950</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4022,22 +3945,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>09:46</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>09:46</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4046,77 +3959,64 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119382414</v>
+        <v>127743814</v>
       </c>
       <c r="B32" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Norr Heden, Norr Heden, Dlr</t>
+          <t>Heden, Heden, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>481955</v>
+        <v>481932</v>
       </c>
       <c r="R32" t="n">
-        <v>6781966</v>
+        <v>6781974</v>
       </c>
       <c r="S32" t="n">
         <v>9</v>
@@ -4143,22 +4043,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4173,27 +4073,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119382367</v>
+        <v>127743928</v>
       </c>
       <c r="B33" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4201,43 +4096,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Norr Heden, Norr Heden, Dlr</t>
+          <t>Hed, Hed, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>481955</v>
+        <v>481947</v>
       </c>
       <c r="R33" t="n">
-        <v>6781965</v>
+        <v>6782029</v>
       </c>
       <c r="S33" t="n">
         <v>9</v>
@@ -4264,22 +4150,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4294,27 +4180,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119382028</v>
+        <v>128505885</v>
       </c>
       <c r="B34" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4339,29 +4220,20 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Heden, Dlr</t>
+          <t>Heden, Heden, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>481933</v>
+        <v>481928</v>
       </c>
       <c r="R34" t="n">
-        <v>6781977</v>
+        <v>6781979</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4385,22 +4257,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4420,22 +4292,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Bo karlstens, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119382056</v>
+        <v>104286688</v>
       </c>
       <c r="B35" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4443,26 +4310,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4470,19 +4337,21 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Norr Heden, Norr Heden, Dlr</t>
+          <t>N Heden, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>481918</v>
+        <v>481961</v>
       </c>
       <c r="R35" t="n">
-        <v>6781971</v>
+        <v>6781987</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4506,22 +4375,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>09:37</t>
+          <t>2022-10-23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>09:37</t>
+          <t>2022-10-23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4530,60 +4389,56 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119382189</v>
+        <v>119039946</v>
       </c>
       <c r="B36" t="n">
-        <v>91828</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>149</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4591,19 +4446,21 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Norr Heden, Norr Heden, Dlr</t>
+          <t>Unänget, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>481915</v>
+        <v>481970</v>
       </c>
       <c r="R36" t="n">
-        <v>6781923</v>
+        <v>6781999</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4627,22 +4484,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>09:41</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>09:41</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4651,33 +4498,29 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119382427</v>
+        <v>119168914</v>
       </c>
       <c r="B37" t="n">
-        <v>88153</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4685,21 +4528,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4708,14 +4551,14 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Heden, Heden, Dlr</t>
+          <t>Heden, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>481946</v>
+        <v>481934</v>
       </c>
       <c r="R37" t="n">
-        <v>6781952</v>
+        <v>6782015</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4742,22 +4585,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4778,60 +4611,58 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119382026</v>
+        <v>119168985</v>
       </c>
       <c r="B38" t="n">
-        <v>90057</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2051</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Norr Heden, Norr Heden, Dlr</t>
+          <t>Heden, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>481916</v>
+        <v>481933</v>
       </c>
       <c r="R38" t="n">
-        <v>6781966</v>
+        <v>6781977</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4855,22 +4686,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>09:34</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>09:34</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4879,37 +4700,33 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119561475</v>
+        <v>119168990</v>
       </c>
       <c r="B39" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4930,29 +4747,23 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Unänget, Unänget, Dlr</t>
+          <t>Heden, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>481919</v>
+        <v>481934</v>
       </c>
       <c r="R39" t="n">
-        <v>6781936</v>
+        <v>6781978</v>
       </c>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4976,22 +4787,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>12:24</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>12:24</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5000,33 +4801,29 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119611893</v>
+        <v>119169099</v>
       </c>
       <c r="B40" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5034,37 +4831,44 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Jäsmyren, Dlr</t>
+          <t>Heden, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>481890</v>
+        <v>481951</v>
       </c>
       <c r="R40" t="n">
         <v>6781976</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5088,17 +4892,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>10 fkr</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5107,33 +4906,29 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119611894</v>
+        <v>119169125</v>
       </c>
       <c r="B41" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5141,37 +4936,44 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Jäsmyren, Dlr</t>
+          <t>Heden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>481888</v>
+        <v>481948</v>
       </c>
       <c r="R41" t="n">
-        <v>6781967</v>
+        <v>6781969</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5195,12 +4997,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5209,33 +5011,29 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119611895</v>
+        <v>119382414</v>
       </c>
       <c r="B42" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5243,37 +5041,46 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Jäsmyren, Dlr</t>
+          <t>Norr Heden, Norr Heden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>481909</v>
+        <v>481955</v>
       </c>
       <c r="R42" t="n">
-        <v>6781959</v>
+        <v>6781966</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5297,17 +5104,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>3fkr</t>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5327,22 +5139,17 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119611892</v>
+        <v>119561475</v>
       </c>
       <c r="B43" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5350,37 +5157,46 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Jäsmyren, Dlr</t>
+          <t>Unänget, Unänget, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>481886</v>
+        <v>481919</v>
       </c>
       <c r="R43" t="n">
-        <v>6781973</v>
+        <v>6781936</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5407,14 +5223,19 @@
           <t>2024-09-05</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-05</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>20 fkr</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5429,27 +5250,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119611898</v>
+        <v>119611902</v>
       </c>
       <c r="B44" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5457,21 +5273,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5481,10 +5297,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>481943</v>
+        <v>481962</v>
       </c>
       <c r="R44" t="n">
-        <v>6781924</v>
+        <v>6782000</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5521,7 +5337,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>4fkr</t>
+          <t>10 fkr</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5548,15 +5364,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119611901</v>
+        <v>119710843</v>
       </c>
       <c r="B45" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5564,21 +5375,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5588,10 +5399,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481908</v>
+        <v>481954</v>
       </c>
       <c r="R45" t="n">
-        <v>6781965</v>
+        <v>6781955</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5626,11 +5437,6 @@
           <t>2024-09-05</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>3fkr</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5643,27 +5449,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119611897</v>
+        <v>125153448</v>
       </c>
       <c r="B46" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5671,34 +5472,43 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Jäsmyren, Dlr</t>
+          <t>Unänget, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>481923</v>
+        <v>481960</v>
       </c>
       <c r="R46" t="n">
-        <v>6781922</v>
+        <v>6782003</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5725,12 +5535,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5745,31 +5565,26 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119611902</v>
+        <v>127743837</v>
       </c>
       <c r="B47" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5793,17 +5608,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Jäsmyren, Dlr</t>
+          <t>Heden, Heden, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481962</v>
+        <v>481926</v>
       </c>
       <c r="R47" t="n">
-        <v>6782000</v>
+        <v>6781984</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5827,17 +5642,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>10 fkr</t>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5852,27 +5672,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119710837</v>
+        <v>127743906</v>
       </c>
       <c r="B48" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5880,37 +5695,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Jäsmyren, Dlr</t>
+          <t>Hed, Hed, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481902</v>
+        <v>481947</v>
       </c>
       <c r="R48" t="n">
-        <v>6781950</v>
+        <v>6782029</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5934,12 +5749,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Flera</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5954,31 +5784,26 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119710843</v>
+        <v>128505711</v>
       </c>
       <c r="B49" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -5999,20 +5824,29 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Jäsmyren, Dlr</t>
+          <t>Heden, Heden, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481954</v>
+        <v>481965</v>
       </c>
       <c r="R49" t="n">
-        <v>6781955</v>
+        <v>6781946</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6036,12 +5870,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6056,22 +5900,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125153302</v>
+        <v>128505792</v>
       </c>
       <c r="B50" t="n">
-        <v>78967</v>
+        <v>93197</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6079,43 +5923,43 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Unänget, Dlr</t>
+          <t>Heden, Heden, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>481960</v>
+        <v>481948</v>
       </c>
       <c r="R50" t="n">
-        <v>6782003</v>
+        <v>6781929</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6142,22 +5986,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6172,69 +6016,63 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125153448</v>
+        <v>119382427</v>
       </c>
       <c r="B51" t="n">
-        <v>92509</v>
+        <v>90522</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr. : Fr.) Kühner</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Unänget, Dlr</t>
+          <t>Heden, Heden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>481960</v>
+        <v>481946</v>
       </c>
       <c r="R51" t="n">
-        <v>6782003</v>
+        <v>6781952</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6258,22 +6096,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6282,28 +6120,29 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127743814</v>
+        <v>104286582</v>
       </c>
       <c r="B52" t="n">
-        <v>92734</v>
+        <v>93235</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6311,37 +6150,48 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Heden, Heden, Dlr</t>
+          <t>N Heden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>481932</v>
+        <v>481927</v>
       </c>
       <c r="R52" t="n">
-        <v>6781974</v>
+        <v>6781938</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6365,22 +6215,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>17:41</t>
+          <t>2022-10-23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>17:41</t>
+          <t>2022-10-23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6389,66 +6229,76 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127743837</v>
+        <v>128505843</v>
       </c>
       <c r="B53" t="n">
-        <v>92742</v>
+        <v>93235</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Heden, Heden, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>481926</v>
+        <v>481924</v>
       </c>
       <c r="R53" t="n">
-        <v>6781984</v>
+        <v>6781967</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6472,22 +6322,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6507,17 +6357,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128505885</v>
+        <v>128505857</v>
       </c>
       <c r="B54" t="n">
-        <v>92803</v>
+        <v>93235</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6525,24 +6375,33 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Heden, Heden, Dlr</t>
@@ -6621,10 +6480,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128505843</v>
+        <v>128712673</v>
       </c>
       <c r="B55" t="n">
-        <v>92849</v>
+        <v>93235</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6649,29 +6508,20 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Heden, Heden, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481924</v>
+        <v>481932</v>
       </c>
       <c r="R55" t="n">
-        <v>6781967</v>
+        <v>6781901</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6695,22 +6545,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6730,61 +6580,52 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128505792</v>
+        <v>128712893</v>
       </c>
       <c r="B56" t="n">
-        <v>92811</v>
+        <v>93235</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Heden, Heden, Dlr</t>
+          <t>Hed, Hed, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>481948</v>
+        <v>481950</v>
       </c>
       <c r="R56" t="n">
-        <v>6781929</v>
+        <v>6782002</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6811,22 +6652,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6846,64 +6687,64 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128505711</v>
+        <v>125153302</v>
       </c>
       <c r="B57" t="n">
-        <v>92811</v>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Heden, Heden, Dlr</t>
+          <t>Unänget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>481965</v>
+        <v>481960</v>
       </c>
       <c r="R57" t="n">
-        <v>6781946</v>
+        <v>6782003</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6927,22 +6768,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6957,22 +6798,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128505857</v>
+        <v>119039963</v>
       </c>
       <c r="B58" t="n">
-        <v>92849</v>
+        <v>79946</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6980,43 +6821,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Heden, Heden, Dlr</t>
+          <t>Unänget, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>481928</v>
+        <v>481902</v>
       </c>
       <c r="R58" t="n">
-        <v>6781979</v>
+        <v>6781960</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7043,22 +6878,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>17:14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>17:14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7067,66 +6892,75 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128505903</v>
+        <v>119169048</v>
       </c>
       <c r="B59" t="n">
-        <v>92836</v>
+        <v>57950</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3100</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Heden, Heden, Dlr</t>
+          <t>Heden, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>481928</v>
+        <v>481942</v>
       </c>
       <c r="R59" t="n">
-        <v>6781979</v>
+        <v>6781931</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7150,22 +6984,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>17:14</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>17:14</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7185,46 +7009,64 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128505947</v>
+        <v>119039990</v>
       </c>
       <c r="B60" t="n">
-        <v>92840</v>
+        <v>8455</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5449</v>
+        <v>106545</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Hed, Hed, Dlr</t>
+          <t>Unänget, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>481948</v>
+        <v>481947</v>
       </c>
       <c r="R60" t="n">
-        <v>6782016</v>
+        <v>6781935</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7248,22 +7090,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>17:14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>17:14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7272,66 +7104,76 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128505610</v>
+        <v>119169051</v>
       </c>
       <c r="B61" t="n">
-        <v>91014</v>
+        <v>8455</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2051</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Heden, Heden, Dlr</t>
+          <t>Heden, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>481963</v>
+        <v>481942</v>
       </c>
       <c r="R61" t="n">
-        <v>6781979</v>
+        <v>6781931</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7355,22 +7197,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>15:54</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>15:54</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7379,6 +7211,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7390,64 +7223,59 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128505815</v>
+        <v>119168995</v>
       </c>
       <c r="B62" t="n">
-        <v>92799</v>
+        <v>99781</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>149</v>
+        <v>222309</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Backstarr</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Carex ericetorum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Heden, Heden, Dlr</t>
+          <t>Heden, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>481917</v>
+        <v>481914</v>
       </c>
       <c r="R62" t="n">
-        <v>6781923</v>
+        <v>6781934</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7471,22 +7299,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>17:14</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>17:14</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7495,6 +7313,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7506,64 +7325,59 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128505701</v>
+        <v>119168998</v>
       </c>
       <c r="B63" t="n">
-        <v>91014</v>
+        <v>99781</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2051</v>
+        <v>222309</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Backstarr</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Carex ericetorum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Heden, Heden, Dlr</t>
+          <t>Heden, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>481965</v>
+        <v>481913</v>
       </c>
       <c r="R63" t="n">
-        <v>6781946</v>
+        <v>6781940</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7587,22 +7401,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>17:08</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>17:08</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7611,6 +7415,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7622,17 +7427,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128619138</v>
+        <v>119169013</v>
       </c>
       <c r="B64" t="n">
-        <v>92844</v>
+        <v>99781</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7640,37 +7445,41 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3100</v>
+        <v>222309</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Backstarr</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Carex ericetorum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Heden, Heden, Dlr</t>
+          <t>Heden, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>481932</v>
+        <v>481920</v>
       </c>
       <c r="R64" t="n">
-        <v>6781995</v>
+        <v>6781960</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7694,22 +7503,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>15:12</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>15:12</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7718,6 +7517,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7729,55 +7529,59 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128619237</v>
+        <v>119169019</v>
       </c>
       <c r="B65" t="n">
-        <v>91028</v>
+        <v>99781</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>256703</v>
+        <v>222309</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Backstarr</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Carex ericetorum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Hed, Hed, Dlr</t>
+          <t>Heden, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>481932</v>
+        <v>481920</v>
       </c>
       <c r="R65" t="n">
-        <v>6782005</v>
+        <v>6781968</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7801,22 +7605,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>15:22</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>15:22</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7825,6 +7619,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7836,17 +7631,17 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128619059</v>
+        <v>119168889</v>
       </c>
       <c r="B66" t="n">
-        <v>92835</v>
+        <v>91402</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7854,34 +7649,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2059</v>
+        <v>256703</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Heden, Heden, Dlr</t>
+          <t>Heden, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>481938</v>
+        <v>481930</v>
       </c>
       <c r="R66" t="n">
-        <v>6781942</v>
+        <v>6782015</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7908,22 +7706,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>15:12</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>15:12</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7932,6 +7720,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7943,17 +7732,17 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128712783</v>
+        <v>128619237</v>
       </c>
       <c r="B67" t="n">
-        <v>91035</v>
+        <v>91402</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7961,33 +7750,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5734</v>
+        <v>256703</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Druvfingersvampar</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramaria botrytis s.lat.</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Heden, Hed, Dlr</t>
+          <t>Hed, Hed, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>481950</v>
+        <v>481932</v>
       </c>
       <c r="R67" t="n">
-        <v>6782002</v>
+        <v>6782005</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8011,22 +7804,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8050,113 +7843,6 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>128712893</v>
-      </c>
-      <c r="B68" t="n">
-        <v>92873</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>5966</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Motaggsvamp</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>Hed, Hed, Dlr</t>
-        </is>
-      </c>
-      <c r="Q68" t="n">
-        <v>481950</v>
-      </c>
-      <c r="R68" t="n">
-        <v>6782002</v>
-      </c>
-      <c r="S68" t="n">
-        <v>10</v>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>Orsa</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>Orsa</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="AD68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT68" t="inlineStr"/>
-      <c r="AW68" t="inlineStr">
-        <is>
-          <t>Bengt Oldhammer</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AZ67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119382189</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128505815</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1037,6 +1052,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67602592</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1171,6 +1191,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112073185</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1280,6 +1305,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119039859</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1389,6 +1419,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119039877</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1498,6 +1533,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119039899</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1599,6 +1639,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119168967</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1700,6 +1745,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119169080</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1801,6 +1851,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119169083</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1908,6 +1963,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119382026</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2015,6 +2075,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128505610</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2131,6 +2196,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128505701</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2240,6 +2310,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104286577</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2356,6 +2431,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119382046</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2458,6 +2538,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611898</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2565,6 +2650,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128619059</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2672,6 +2762,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128505903</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2779,6 +2874,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128619138</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2888,6 +2988,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112074852</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2989,6 +3094,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119168904</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3094,6 +3204,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119168950</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3199,6 +3314,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119168971</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3300,6 +3420,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119168977</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3416,6 +3541,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119382028</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3532,6 +3662,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119382056</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3648,6 +3783,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119382060</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3764,6 +3904,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119559723</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3866,6 +4011,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611901</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3975,6 +4125,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119710835</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4082,6 +4237,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127743814</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4189,6 +4349,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127743928</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4296,6 +4461,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128505885</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4405,6 +4575,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104286688</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4514,6 +4689,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119039946</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4615,6 +4795,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119168914</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4716,6 +4901,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119168985</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4817,6 +5007,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119168990</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4922,6 +5117,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119169099</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5027,6 +5227,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119169125</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5143,6 +5348,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119382414</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5259,6 +5469,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119561475</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5361,6 +5576,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611902</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5458,6 +5678,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119710843</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5574,6 +5799,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125153448</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5681,6 +5911,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127743837</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5793,6 +6028,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127743906</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5909,6 +6149,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128505711</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6025,6 +6270,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128505792</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6136,6 +6386,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119382427</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6245,6 +6500,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104286582</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6361,6 +6621,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128505843</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6477,6 +6742,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128505857</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6584,6 +6854,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128712673</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6691,6 +6966,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128712893</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6807,6 +7087,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125153302</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6908,6 +7193,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119039963</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7013,6 +7303,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119169048</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7120,6 +7415,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119039990</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7227,6 +7527,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119169051</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7329,6 +7634,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119168995</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7431,6 +7741,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119168998</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7533,6 +7848,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119169013</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7635,6 +7955,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119169019</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7736,6 +8061,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119168889</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7843,8 +8173,81 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128619237</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -1544,7 +1544,7 @@
         <v>119168967</v>
       </c>
       <c r="B9" t="n">
-        <v>91394</v>
+        <v>91533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>119169080</v>
       </c>
       <c r="B10" t="n">
-        <v>91394</v>
+        <v>91533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>119169083</v>
       </c>
       <c r="B11" t="n">
-        <v>91394</v>
+        <v>91533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>119382026</v>
       </c>
       <c r="B12" t="n">
-        <v>91394</v>
+        <v>91533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ67"/>
+  <dimension ref="A1:AZ68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8176,6 +8176,118 @@
       <c r="AZ67" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128619237</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>136024097</v>
+      </c>
+      <c r="B68" t="n">
+        <v>91541</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Tallås N Hedens återvinningscentral, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>481964</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6782031</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136024097</t>
         </is>
       </c>
     </row>
@@ -8247,6 +8359,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -1544,7 +1544,7 @@
         <v>119168967</v>
       </c>
       <c r="B9" t="n">
-        <v>91533</v>
+        <v>91535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>119169080</v>
       </c>
       <c r="B10" t="n">
-        <v>91533</v>
+        <v>91535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>119169083</v>
       </c>
       <c r="B11" t="n">
-        <v>91533</v>
+        <v>91535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>119382026</v>
       </c>
       <c r="B12" t="n">
-        <v>91533</v>
+        <v>91535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>136024097</v>
       </c>
       <c r="B68" t="n">
-        <v>91541</v>
+        <v>91543</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -1544,7 +1544,7 @@
         <v>119168967</v>
       </c>
       <c r="B9" t="n">
-        <v>91535</v>
+        <v>91536</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>119169080</v>
       </c>
       <c r="B10" t="n">
-        <v>91535</v>
+        <v>91536</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>119169083</v>
       </c>
       <c r="B11" t="n">
-        <v>91535</v>
+        <v>91536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>119382026</v>
       </c>
       <c r="B12" t="n">
-        <v>91535</v>
+        <v>91536</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>136024097</v>
       </c>
       <c r="B68" t="n">
-        <v>91543</v>
+        <v>91544</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -1544,7 +1544,7 @@
         <v>119168967</v>
       </c>
       <c r="B9" t="n">
-        <v>91536</v>
+        <v>91537</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>119169080</v>
       </c>
       <c r="B10" t="n">
-        <v>91536</v>
+        <v>91537</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>119169083</v>
       </c>
       <c r="B11" t="n">
-        <v>91536</v>
+        <v>91537</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>119382026</v>
       </c>
       <c r="B12" t="n">
-        <v>91536</v>
+        <v>91537</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>136024097</v>
       </c>
       <c r="B68" t="n">
-        <v>91544</v>
+        <v>91545</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -1544,7 +1544,7 @@
         <v>119168967</v>
       </c>
       <c r="B9" t="n">
-        <v>91537</v>
+        <v>91538</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>119169080</v>
       </c>
       <c r="B10" t="n">
-        <v>91537</v>
+        <v>91538</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>119169083</v>
       </c>
       <c r="B11" t="n">
-        <v>91537</v>
+        <v>91538</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>119382026</v>
       </c>
       <c r="B12" t="n">
-        <v>91537</v>
+        <v>91538</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>136024097</v>
       </c>
       <c r="B68" t="n">
-        <v>91545</v>
+        <v>91546</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -1544,7 +1544,7 @@
         <v>119168967</v>
       </c>
       <c r="B9" t="n">
-        <v>91538</v>
+        <v>91544</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>119169080</v>
       </c>
       <c r="B10" t="n">
-        <v>91538</v>
+        <v>91544</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>119169083</v>
       </c>
       <c r="B11" t="n">
-        <v>91538</v>
+        <v>91544</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>119382026</v>
       </c>
       <c r="B12" t="n">
-        <v>91538</v>
+        <v>91544</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>136024097</v>
       </c>
       <c r="B68" t="n">
-        <v>91546</v>
+        <v>91552</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -1544,7 +1544,7 @@
         <v>119168967</v>
       </c>
       <c r="B9" t="n">
-        <v>91544</v>
+        <v>91545</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>119169080</v>
       </c>
       <c r="B10" t="n">
-        <v>91544</v>
+        <v>91545</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>119169083</v>
       </c>
       <c r="B11" t="n">
-        <v>91544</v>
+        <v>91545</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>119382026</v>
       </c>
       <c r="B12" t="n">
-        <v>91544</v>
+        <v>91545</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>136024097</v>
       </c>
       <c r="B68" t="n">
-        <v>91552</v>
+        <v>91553</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -1544,7 +1544,7 @@
         <v>119168967</v>
       </c>
       <c r="B9" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>119169080</v>
       </c>
       <c r="B10" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>119169083</v>
       </c>
       <c r="B11" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>119382026</v>
       </c>
       <c r="B12" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>136024097</v>
       </c>
       <c r="B68" t="n">
-        <v>91553</v>
+        <v>91559</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -1544,7 +1544,7 @@
         <v>119168967</v>
       </c>
       <c r="B9" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>119169080</v>
       </c>
       <c r="B10" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>119169083</v>
       </c>
       <c r="B11" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>119382026</v>
       </c>
       <c r="B12" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>136024097</v>
       </c>
       <c r="B68" t="n">
-        <v>91559</v>
+        <v>91566</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -1544,7 +1544,7 @@
         <v>119168967</v>
       </c>
       <c r="B9" t="n">
-        <v>91558</v>
+        <v>91559</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>119169080</v>
       </c>
       <c r="B10" t="n">
-        <v>91558</v>
+        <v>91559</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>119169083</v>
       </c>
       <c r="B11" t="n">
-        <v>91558</v>
+        <v>91559</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>119382026</v>
       </c>
       <c r="B12" t="n">
-        <v>91558</v>
+        <v>91559</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>136024097</v>
       </c>
       <c r="B68" t="n">
-        <v>91566</v>
+        <v>91567</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -1544,7 +1544,7 @@
         <v>119168967</v>
       </c>
       <c r="B9" t="n">
-        <v>91559</v>
+        <v>91572</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>119169080</v>
       </c>
       <c r="B10" t="n">
-        <v>91559</v>
+        <v>91572</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>119169083</v>
       </c>
       <c r="B11" t="n">
-        <v>91559</v>
+        <v>91572</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>119382026</v>
       </c>
       <c r="B12" t="n">
-        <v>91559</v>
+        <v>91572</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>136024097</v>
       </c>
       <c r="B68" t="n">
-        <v>91567</v>
+        <v>91580</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ68"/>
+  <dimension ref="A1:AZ80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -922,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>67602592</v>
+        <v>136557010</v>
       </c>
       <c r="B4" t="n">
-        <v>91394</v>
+        <v>92895</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,26 +933,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2051</v>
+        <v>1958</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -960,17 +960,16 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bjus, 1 km NNO Ribbygget, Dlr</t>
+          <t>Tallås N Hedens återvinningscentral, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481970</v>
+        <v>481938</v>
       </c>
       <c r="R4" t="n">
-        <v>6782001</v>
+        <v>6782020</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -997,12 +996,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-09-14</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-09-14</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,81 +1020,55 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>ås med äldre tall</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67602592</t>
+          <t>https://artportalen.se/Sighting/136557010</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112073185</v>
+        <v>136557003</v>
       </c>
       <c r="B5" t="n">
-        <v>91394</v>
+        <v>93434</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2051</v>
+        <v>1968</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1093,23 +1076,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Unänget, Dlr</t>
+          <t>Tallås N Hedens återvinningscentral, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481940</v>
+        <v>481924</v>
       </c>
       <c r="R5" t="n">
-        <v>6782037</v>
+        <v>6781955</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1136,12 +1115,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På sandtall mark</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,52 +1148,27 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>ås</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112073185</t>
+          <t>https://artportalen.se/Sighting/136557003</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119039859</v>
+        <v>67602592</v>
       </c>
       <c r="B6" t="n">
         <v>91394</v>
@@ -1234,24 +1203,23 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Unänget, Dlr</t>
+          <t>Bjus, 1 km NNO Ribbygget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481974</v>
+        <v>481970</v>
       </c>
       <c r="R6" t="n">
-        <v>6781922</v>
+        <v>6782001</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1275,12 +1243,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2017-09-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2017-09-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1293,27 +1261,52 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>ås med äldre tall</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119039859</t>
+          <t>https://artportalen.se/Sighting/67602592</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119039877</v>
+        <v>112073185</v>
       </c>
       <c r="B7" t="n">
         <v>91394</v>
@@ -1348,7 +1341,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1359,13 +1352,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481926</v>
+        <v>481940</v>
       </c>
       <c r="R7" t="n">
-        <v>6781971</v>
+        <v>6782037</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1389,12 +1382,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1407,27 +1400,52 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>ås</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119039877</t>
+          <t>https://artportalen.se/Sighting/112073185</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119039899</v>
+        <v>119039859</v>
       </c>
       <c r="B8" t="n">
         <v>91394</v>
@@ -1473,10 +1491,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481970</v>
+        <v>481974</v>
       </c>
       <c r="R8" t="n">
-        <v>6781999</v>
+        <v>6781922</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1535,16 +1553,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119039899</t>
+          <t>https://artportalen.se/Sighting/119039859</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119168967</v>
+        <v>119039877</v>
       </c>
       <c r="B9" t="n">
-        <v>91572</v>
+        <v>91394</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,23 +1587,31 @@
           <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Heden, Dlr</t>
+          <t>Unänget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481930</v>
+        <v>481926</v>
       </c>
       <c r="R9" t="n">
-        <v>6781990</v>
+        <v>6781971</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1609,12 +1635,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1630,27 +1656,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119168967</t>
+          <t>https://artportalen.se/Sighting/119039877</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119169080</v>
+        <v>119039899</v>
       </c>
       <c r="B10" t="n">
-        <v>91572</v>
+        <v>91394</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1675,23 +1701,31 @@
           <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Heden, Dlr</t>
+          <t>Unänget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481977</v>
+        <v>481970</v>
       </c>
       <c r="R10" t="n">
-        <v>6781965</v>
+        <v>6781999</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1715,12 +1749,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1736,27 +1770,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119169080</t>
+          <t>https://artportalen.se/Sighting/119039899</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119169083</v>
+        <v>119168967</v>
       </c>
       <c r="B11" t="n">
-        <v>91572</v>
+        <v>91573</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1791,10 +1825,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481984</v>
+        <v>481930</v>
       </c>
       <c r="R11" t="n">
-        <v>6781944</v>
+        <v>6781990</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1853,16 +1887,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119169083</t>
+          <t>https://artportalen.se/Sighting/119168967</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119382026</v>
+        <v>119169080</v>
       </c>
       <c r="B12" t="n">
-        <v>91572</v>
+        <v>91573</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1888,19 +1922,22 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norr Heden, Norr Heden, Dlr</t>
+          <t>Heden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481916</v>
+        <v>481977</v>
       </c>
       <c r="R12" t="n">
-        <v>6781966</v>
+        <v>6781965</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1924,22 +1961,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:34</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:34</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1948,33 +1975,34 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119382026</t>
+          <t>https://artportalen.se/Sighting/119169080</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128505610</v>
+        <v>119169083</v>
       </c>
       <c r="B13" t="n">
-        <v>91394</v>
+        <v>91573</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2000,19 +2028,22 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Heden, Heden, Dlr</t>
+          <t>Heden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481963</v>
+        <v>481984</v>
       </c>
       <c r="R13" t="n">
-        <v>6781979</v>
+        <v>6781944</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2036,22 +2067,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:54</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:54</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2060,6 +2081,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2071,22 +2093,22 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128505610</t>
+          <t>https://artportalen.se/Sighting/119169083</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128505701</v>
+        <v>119382026</v>
       </c>
       <c r="B14" t="n">
-        <v>91394</v>
+        <v>91573</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2111,29 +2133,20 @@
           <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Heden, Heden, Dlr</t>
+          <t>Norr Heden, Norr Heden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481965</v>
+        <v>481916</v>
       </c>
       <c r="R14" t="n">
-        <v>6781946</v>
+        <v>6781966</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2157,22 +2170,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2187,27 +2200,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128505701</t>
+          <t>https://artportalen.se/Sighting/119382026</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104286577</v>
+        <v>128505610</v>
       </c>
       <c r="B15" t="n">
-        <v>93213</v>
+        <v>91394</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,48 +2228,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2059</v>
+        <v>2051</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>N Heden, Dlr</t>
+          <t>Heden, Heden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481927</v>
+        <v>481963</v>
       </c>
       <c r="R15" t="n">
-        <v>6781938</v>
+        <v>6781979</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2280,12 +2282,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2294,34 +2306,33 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104286577</t>
+          <t>https://artportalen.se/Sighting/128505610</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119382046</v>
+        <v>128505701</v>
       </c>
       <c r="B16" t="n">
-        <v>93213</v>
+        <v>91394</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2329,21 +2340,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2059</v>
+        <v>2051</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2358,17 +2369,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norr Heden, Norr Heden, Dlr</t>
+          <t>Heden, Heden, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481916</v>
+        <v>481965</v>
       </c>
       <c r="R16" t="n">
-        <v>6781966</v>
+        <v>6781946</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2392,22 +2403,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2422,24 +2433,24 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119382046</t>
+          <t>https://artportalen.se/Sighting/128505701</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119611898</v>
+        <v>104286577</v>
       </c>
       <c r="B17" t="n">
         <v>93213</v>
@@ -2467,20 +2478,31 @@
           <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Jäsmyren, Dlr</t>
+          <t>N Heden, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481943</v>
+        <v>481927</v>
       </c>
       <c r="R17" t="n">
-        <v>6781924</v>
+        <v>6781938</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2504,17 +2526,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2022-10-23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>4fkr</t>
+          <t>2022-10-23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2523,30 +2540,31 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119611898</t>
+          <t>https://artportalen.se/Sighting/104286577</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128619059</v>
+        <v>119382046</v>
       </c>
       <c r="B18" t="n">
         <v>93213</v>
@@ -2574,20 +2592,29 @@
           <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Heden, Heden, Dlr</t>
+          <t>Norr Heden, Norr Heden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481938</v>
+        <v>481916</v>
       </c>
       <c r="R18" t="n">
-        <v>6781942</v>
+        <v>6781966</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2611,22 +2638,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2641,62 +2668,62 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128619059</t>
+          <t>https://artportalen.se/Sighting/119382046</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128505903</v>
+        <v>119611898</v>
       </c>
       <c r="B19" t="n">
-        <v>93222</v>
+        <v>93213</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3100</v>
+        <v>2059</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Heden, Heden, Dlr</t>
+          <t>Jäsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481928</v>
+        <v>481943</v>
       </c>
       <c r="R19" t="n">
-        <v>6781979</v>
+        <v>6781924</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2723,22 +2750,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>17:14</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>17:14</t>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>4fkr</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2753,49 +2775,49 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128505903</t>
+          <t>https://artportalen.se/Sighting/119611898</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128619138</v>
+        <v>128619059</v>
       </c>
       <c r="B20" t="n">
-        <v>93222</v>
+        <v>93213</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3100</v>
+        <v>2059</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2805,13 +2827,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481932</v>
+        <v>481938</v>
       </c>
       <c r="R20" t="n">
-        <v>6781995</v>
+        <v>6781942</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2870,22 +2892,22 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128619138</t>
+          <t>https://artportalen.se/Sighting/128619059</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112074852</v>
+        <v>128505903</v>
       </c>
       <c r="B21" t="n">
-        <v>93189</v>
+        <v>93222</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2893,45 +2915,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(J.C.Schmidt) Baird</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Norr Heden, Dlr</t>
+          <t>Heden, Heden, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481940</v>
+        <v>481928</v>
       </c>
       <c r="R21" t="n">
-        <v>6782037</v>
+        <v>6781979</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2958,12 +2969,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2972,34 +2993,33 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist, Janolof Hermansson</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112074852</t>
+          <t>https://artportalen.se/Sighting/128505903</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119168904</v>
+        <v>128619138</v>
       </c>
       <c r="B22" t="n">
-        <v>93189</v>
+        <v>93222</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3007,40 +3027,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Heden, Dlr</t>
+          <t>Heden, Heden, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481935</v>
+        <v>481932</v>
       </c>
       <c r="R22" t="n">
-        <v>6782015</v>
+        <v>6781995</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3064,12 +3081,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3078,7 +3105,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3090,22 +3116,22 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119168904</t>
+          <t>https://artportalen.se/Sighting/128619138</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119168950</v>
+        <v>136557002</v>
       </c>
       <c r="B23" t="n">
-        <v>93189</v>
+        <v>93425</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3113,44 +3139,41 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Heden, Dlr</t>
+          <t>Tallås N Hedens återvinningscentral, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481942</v>
+        <v>481924</v>
       </c>
       <c r="R23" t="n">
-        <v>6782014</v>
+        <v>6781955</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3174,12 +3197,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3188,31 +3221,30 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119168950</t>
+          <t>https://artportalen.se/Sighting/136557002</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119168971</v>
+        <v>112074852</v>
       </c>
       <c r="B24" t="n">
         <v>93189</v>
@@ -3242,25 +3274,29 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Heden, Dlr</t>
+          <t>Norr Heden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481927</v>
+        <v>481940</v>
       </c>
       <c r="R24" t="n">
-        <v>6781985</v>
+        <v>6782037</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3284,12 +3320,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3305,24 +3341,24 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119168971</t>
+          <t>https://artportalen.se/Sighting/112074852</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119168977</v>
+        <v>119168904</v>
       </c>
       <c r="B25" t="n">
         <v>93189</v>
@@ -3360,13 +3396,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481983</v>
+        <v>481935</v>
       </c>
       <c r="R25" t="n">
-        <v>6781927</v>
+        <v>6782015</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3422,13 +3458,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119168977</t>
+          <t>https://artportalen.se/Sighting/119168904</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119382028</v>
+        <v>119168950</v>
       </c>
       <c r="B26" t="n">
         <v>93189</v>
@@ -3458,24 +3494,22 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Heden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481933</v>
+        <v>481942</v>
       </c>
       <c r="R26" t="n">
-        <v>6781977</v>
+        <v>6782014</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3502,22 +3536,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>09:35</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>09:35</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3526,6 +3550,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3537,19 +3562,19 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Bo karlstens, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119382028</t>
+          <t>https://artportalen.se/Sighting/119168950</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119382056</v>
+        <v>119168971</v>
       </c>
       <c r="B27" t="n">
         <v>93189</v>
@@ -3579,27 +3604,25 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norr Heden, Norr Heden, Dlr</t>
+          <t>Heden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481918</v>
+        <v>481927</v>
       </c>
       <c r="R27" t="n">
-        <v>6781971</v>
+        <v>6781985</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3623,22 +3646,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>09:37</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>09:37</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3647,30 +3660,31 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119382056</t>
+          <t>https://artportalen.se/Sighting/119168971</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119382060</v>
+        <v>119168977</v>
       </c>
       <c r="B28" t="n">
         <v>93189</v>
@@ -3698,29 +3712,23 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Heden, Heden, Dlr</t>
+          <t>Heden, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481925</v>
+        <v>481983</v>
       </c>
       <c r="R28" t="n">
-        <v>6781974</v>
+        <v>6781927</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3744,22 +3752,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>09:38</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>09:38</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3768,6 +3766,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3779,19 +3778,19 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Bo karlstens, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119382060</t>
+          <t>https://artportalen.se/Sighting/119168977</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119559723</v>
+        <v>119382028</v>
       </c>
       <c r="B29" t="n">
         <v>93189</v>
@@ -3821,7 +3820,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3831,17 +3830,17 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norr Heden, Norr Heden, Dlr</t>
+          <t>Heden, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481940</v>
+        <v>481933</v>
       </c>
       <c r="R29" t="n">
-        <v>6782025</v>
+        <v>6781977</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3865,22 +3864,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3895,24 +3894,24 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna-Britt Olsson, Erik Danielsson, Lisa Olson, Göran Ehn</t>
+          <t>Bengt Oldhammer, Bo karlstens, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119559723</t>
+          <t>https://artportalen.se/Sighting/119382028</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119611901</v>
+        <v>119382056</v>
       </c>
       <c r="B30" t="n">
         <v>93189</v>
@@ -3940,20 +3939,29 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Jäsmyren, Dlr</t>
+          <t>Norr Heden, Norr Heden, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481908</v>
+        <v>481918</v>
       </c>
       <c r="R30" t="n">
-        <v>6781965</v>
+        <v>6781971</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3977,17 +3985,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>3fkr</t>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4007,19 +4020,19 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119611901</t>
+          <t>https://artportalen.se/Sighting/119382056</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119710835</v>
+        <v>119382060</v>
       </c>
       <c r="B31" t="n">
         <v>93189</v>
@@ -4049,7 +4062,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4057,18 +4070,16 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Jäsmyren, Dlr</t>
+          <t>Heden, Heden, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481902</v>
+        <v>481925</v>
       </c>
       <c r="R31" t="n">
-        <v>6781950</v>
+        <v>6781974</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4095,12 +4106,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4109,31 +4130,30 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bengt Oldhammer, Bo karlstens, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119710835</t>
+          <t>https://artportalen.se/Sighting/119382060</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127743814</v>
+        <v>119559723</v>
       </c>
       <c r="B32" t="n">
         <v>93189</v>
@@ -4161,17 +4181,26 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Heden, Heden, Dlr</t>
+          <t>Norr Heden, Norr Heden, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>481932</v>
+        <v>481940</v>
       </c>
       <c r="R32" t="n">
-        <v>6781974</v>
+        <v>6782025</v>
       </c>
       <c r="S32" t="n">
         <v>9</v>
@@ -4198,22 +4227,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4228,24 +4257,24 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens, Anna-Britt Olsson, Erik Danielsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127743814</t>
+          <t>https://artportalen.se/Sighting/119559723</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127743928</v>
+        <v>119611901</v>
       </c>
       <c r="B33" t="n">
         <v>93189</v>
@@ -4276,17 +4305,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hed, Hed, Dlr</t>
+          <t>Jäsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>481947</v>
+        <v>481908</v>
       </c>
       <c r="R33" t="n">
-        <v>6782029</v>
+        <v>6781965</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4310,22 +4339,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>17:41</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>17:41</t>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>3fkr</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4340,24 +4364,24 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127743928</t>
+          <t>https://artportalen.se/Sighting/119611901</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128505885</v>
+        <v>119710835</v>
       </c>
       <c r="B34" t="n">
         <v>93189</v>
@@ -4385,17 +4409,28 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Heden, Heden, Dlr</t>
+          <t>Jäsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>481928</v>
+        <v>481902</v>
       </c>
       <c r="R34" t="n">
-        <v>6781979</v>
+        <v>6781950</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4422,22 +4457,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>17:14</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>17:14</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4446,33 +4471,34 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128505885</t>
+          <t>https://artportalen.se/Sighting/119710835</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>104286688</v>
+        <v>127743814</v>
       </c>
       <c r="B35" t="n">
-        <v>93197</v>
+        <v>93189</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4480,48 +4506,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>N Heden, Dlr</t>
+          <t>Heden, Heden, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>481961</v>
+        <v>481932</v>
       </c>
       <c r="R35" t="n">
-        <v>6781987</v>
+        <v>6781974</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4545,12 +4560,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4559,34 +4584,33 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104286688</t>
+          <t>https://artportalen.se/Sighting/127743814</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119039946</v>
+        <v>127743928</v>
       </c>
       <c r="B36" t="n">
-        <v>93197</v>
+        <v>93189</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4594,48 +4618,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Unänget, Dlr</t>
+          <t>Hed, Hed, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>481970</v>
+        <v>481947</v>
       </c>
       <c r="R36" t="n">
-        <v>6781999</v>
+        <v>6782029</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4659,12 +4672,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4673,34 +4696,33 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119039946</t>
+          <t>https://artportalen.se/Sighting/127743928</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119168914</v>
+        <v>128505885</v>
       </c>
       <c r="B37" t="n">
-        <v>93197</v>
+        <v>93189</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4708,40 +4730,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Heden, Dlr</t>
+          <t>Heden, Heden, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>481934</v>
+        <v>481928</v>
       </c>
       <c r="R37" t="n">
-        <v>6782015</v>
+        <v>6781979</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4765,12 +4784,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4779,7 +4808,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4791,19 +4819,19 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119168914</t>
+          <t>https://artportalen.se/Sighting/128505885</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119168985</v>
+        <v>104286688</v>
       </c>
       <c r="B38" t="n">
         <v>93197</v>
@@ -4831,23 +4859,31 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Heden, Dlr</t>
+          <t>N Heden, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>481933</v>
+        <v>481961</v>
       </c>
       <c r="R38" t="n">
-        <v>6781977</v>
+        <v>6781987</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4871,12 +4907,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2022-10-23</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2022-10-23</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4892,24 +4928,24 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119168985</t>
+          <t>https://artportalen.se/Sighting/104286688</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119168990</v>
+        <v>119039946</v>
       </c>
       <c r="B39" t="n">
         <v>93197</v>
@@ -4937,23 +4973,31 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Heden, Dlr</t>
+          <t>Unänget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>481934</v>
+        <v>481970</v>
       </c>
       <c r="R39" t="n">
-        <v>6781978</v>
+        <v>6781999</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4977,12 +5021,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4998,24 +5042,24 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119168990</t>
+          <t>https://artportalen.se/Sighting/119039946</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119169099</v>
+        <v>119168914</v>
       </c>
       <c r="B40" t="n">
         <v>93197</v>
@@ -5043,11 +5087,7 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -5057,10 +5097,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>481951</v>
+        <v>481934</v>
       </c>
       <c r="R40" t="n">
-        <v>6781976</v>
+        <v>6782015</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5119,13 +5159,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119169099</t>
+          <t>https://artportalen.se/Sighting/119168914</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119169125</v>
+        <v>119168985</v>
       </c>
       <c r="B41" t="n">
         <v>93197</v>
@@ -5153,11 +5193,7 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
@@ -5167,13 +5203,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>481948</v>
+        <v>481933</v>
       </c>
       <c r="R41" t="n">
-        <v>6781969</v>
+        <v>6781977</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5229,13 +5265,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119169125</t>
+          <t>https://artportalen.se/Sighting/119168985</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119382414</v>
+        <v>119168990</v>
       </c>
       <c r="B42" t="n">
         <v>93197</v>
@@ -5263,29 +5299,23 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Norr Heden, Norr Heden, Dlr</t>
+          <t>Heden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>481955</v>
+        <v>481934</v>
       </c>
       <c r="R42" t="n">
-        <v>6781966</v>
+        <v>6781978</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5309,22 +5339,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>09:51</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>09:51</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5333,30 +5353,31 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119382414</t>
+          <t>https://artportalen.se/Sighting/119168990</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119561475</v>
+        <v>119169099</v>
       </c>
       <c r="B43" t="n">
         <v>93197</v>
@@ -5386,27 +5407,25 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Unänget, Unänget, Dlr</t>
+          <t>Heden, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>481919</v>
+        <v>481951</v>
       </c>
       <c r="R43" t="n">
-        <v>6781936</v>
+        <v>6781976</v>
       </c>
       <c r="S43" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5430,22 +5449,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>12:24</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>12:24</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5454,30 +5463,31 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119561475</t>
+          <t>https://artportalen.se/Sighting/119169099</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119611902</v>
+        <v>119169125</v>
       </c>
       <c r="B44" t="n">
         <v>93197</v>
@@ -5505,20 +5515,27 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Jäsmyren, Dlr</t>
+          <t>Heden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>481962</v>
+        <v>481948</v>
       </c>
       <c r="R44" t="n">
-        <v>6782000</v>
+        <v>6781969</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5542,17 +5559,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>10 fkr</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5561,30 +5573,31 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119611902</t>
+          <t>https://artportalen.se/Sighting/119169125</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119710843</v>
+        <v>119382414</v>
       </c>
       <c r="B45" t="n">
         <v>93197</v>
@@ -5612,20 +5625,29 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Jäsmyren, Dlr</t>
+          <t>Norr Heden, Norr Heden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481954</v>
+        <v>481955</v>
       </c>
       <c r="R45" t="n">
-        <v>6781955</v>
+        <v>6781966</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5649,12 +5671,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5669,24 +5701,24 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119710843</t>
+          <t>https://artportalen.se/Sighting/119382414</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125153448</v>
+        <v>119561475</v>
       </c>
       <c r="B46" t="n">
         <v>93197</v>
@@ -5716,7 +5748,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5726,17 +5758,17 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Unänget, Dlr</t>
+          <t>Unänget, Unänget, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>481960</v>
+        <v>481919</v>
       </c>
       <c r="R46" t="n">
-        <v>6782003</v>
+        <v>6781936</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5760,22 +5792,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5790,24 +5822,24 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125153448</t>
+          <t>https://artportalen.se/Sighting/119561475</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127743837</v>
+        <v>119611902</v>
       </c>
       <c r="B47" t="n">
         <v>93197</v>
@@ -5838,17 +5870,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Heden, Heden, Dlr</t>
+          <t>Jäsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481926</v>
+        <v>481962</v>
       </c>
       <c r="R47" t="n">
-        <v>6781984</v>
+        <v>6782000</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5872,22 +5904,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>17:41</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>17:41</t>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>10 fkr</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5902,24 +5929,24 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127743837</t>
+          <t>https://artportalen.se/Sighting/119611902</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127743906</v>
+        <v>119710843</v>
       </c>
       <c r="B48" t="n">
         <v>93197</v>
@@ -5950,17 +5977,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hed, Hed, Dlr</t>
+          <t>Jäsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481947</v>
+        <v>481954</v>
       </c>
       <c r="R48" t="n">
-        <v>6782029</v>
+        <v>6781955</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5984,27 +6011,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>17:41</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>17:41</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Flera</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6019,24 +6031,24 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127743906</t>
+          <t>https://artportalen.se/Sighting/119710843</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128505711</v>
+        <v>125153448</v>
       </c>
       <c r="B49" t="n">
         <v>93197</v>
@@ -6066,7 +6078,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6076,17 +6088,17 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Heden, Heden, Dlr</t>
+          <t>Unänget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481965</v>
+        <v>481960</v>
       </c>
       <c r="R49" t="n">
-        <v>6781946</v>
+        <v>6782003</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6110,22 +6122,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6140,24 +6152,24 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128505711</t>
+          <t>https://artportalen.se/Sighting/125153448</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128505792</v>
+        <v>127743837</v>
       </c>
       <c r="B50" t="n">
         <v>93197</v>
@@ -6185,29 +6197,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Heden, Heden, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>481948</v>
+        <v>481926</v>
       </c>
       <c r="R50" t="n">
-        <v>6781929</v>
+        <v>6781984</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6231,22 +6234,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6266,22 +6269,22 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128505792</t>
+          <t>https://artportalen.se/Sighting/127743837</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119382427</v>
+        <v>127743906</v>
       </c>
       <c r="B51" t="n">
-        <v>90522</v>
+        <v>93197</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6289,40 +6292,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Heden, Heden, Dlr</t>
+          <t>Hed, Hed, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>481946</v>
+        <v>481947</v>
       </c>
       <c r="R51" t="n">
-        <v>6781952</v>
+        <v>6782029</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6346,22 +6346,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Flera</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6370,7 +6375,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6382,22 +6386,22 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119382427</t>
+          <t>https://artportalen.se/Sighting/127743906</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>104286582</v>
+        <v>128505711</v>
       </c>
       <c r="B52" t="n">
-        <v>93235</v>
+        <v>93197</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6405,26 +6409,26 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6432,21 +6436,19 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>N Heden, Dlr</t>
+          <t>Heden, Heden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>481927</v>
+        <v>481965</v>
       </c>
       <c r="R52" t="n">
-        <v>6781938</v>
+        <v>6781946</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6470,12 +6472,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6484,34 +6496,33 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104286582</t>
+          <t>https://artportalen.se/Sighting/128505711</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128505843</v>
+        <v>128505792</v>
       </c>
       <c r="B53" t="n">
-        <v>93235</v>
+        <v>93197</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6519,26 +6530,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6552,10 +6563,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>481924</v>
+        <v>481948</v>
       </c>
       <c r="R53" t="n">
-        <v>6781967</v>
+        <v>6781929</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6587,7 +6598,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6597,7 +6608,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6623,16 +6634,16 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128505843</t>
+          <t>https://artportalen.se/Sighting/128505792</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128505857</v>
+        <v>136556992</v>
       </c>
       <c r="B54" t="n">
-        <v>93235</v>
+        <v>93400</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6640,46 +6651,41 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Heden, Heden, Dlr</t>
+          <t>Tallås N Hedens återvinningscentral, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>481928</v>
+        <v>481968</v>
       </c>
       <c r="R54" t="n">
-        <v>6781979</v>
+        <v>6781996</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6703,22 +6709,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6733,27 +6739,27 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128505857</t>
+          <t>https://artportalen.se/Sighting/136556992</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128712673</v>
+        <v>136556993</v>
       </c>
       <c r="B55" t="n">
-        <v>93235</v>
+        <v>93400</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6761,34 +6767,43 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Heden, Heden, Dlr</t>
+          <t>Tallås N Hedens återvinningscentral, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481932</v>
+        <v>481953</v>
       </c>
       <c r="R55" t="n">
-        <v>6781901</v>
+        <v>6781968</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6815,22 +6830,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6845,27 +6860,27 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128712673</t>
+          <t>https://artportalen.se/Sighting/136556993</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128712893</v>
+        <v>136556995</v>
       </c>
       <c r="B56" t="n">
-        <v>93235</v>
+        <v>93400</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6873,37 +6888,46 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Hed, Hed, Dlr</t>
+          <t>Tallås N Hedens återvinningscentral, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>481950</v>
+        <v>481941</v>
       </c>
       <c r="R56" t="n">
-        <v>6782002</v>
+        <v>6781925</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6927,22 +6951,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6957,49 +6981,49 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128712893</t>
+          <t>https://artportalen.se/Sighting/136556995</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125153302</v>
+        <v>136556997</v>
       </c>
       <c r="B57" t="n">
-        <v>79327</v>
+        <v>93400</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -7009,22 +7033,22 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Unänget, Dlr</t>
+          <t>Tallås N Hedens återvinningscentral, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>481960</v>
+        <v>481941</v>
       </c>
       <c r="R57" t="n">
-        <v>6782003</v>
+        <v>6781923</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7048,22 +7072,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7078,27 +7102,27 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125153302</t>
+          <t>https://artportalen.se/Sighting/136556997</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119039963</v>
+        <v>136556998</v>
       </c>
       <c r="B58" t="n">
-        <v>79946</v>
+        <v>93400</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7106,40 +7130,46 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Unänget, Dlr</t>
+          <t>Tallås N Hedens återvinningscentral, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>481902</v>
+        <v>481938</v>
       </c>
       <c r="R58" t="n">
-        <v>6781960</v>
+        <v>6781925</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7163,12 +7193,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7177,80 +7217,80 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119039963</t>
+          <t>https://artportalen.se/Sighting/136556998</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119169048</v>
+        <v>136556999</v>
       </c>
       <c r="B59" t="n">
-        <v>57950</v>
+        <v>93400</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Heden, Dlr</t>
+          <t>Tallås N Hedens återvinningscentral, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>481942</v>
+        <v>481925</v>
       </c>
       <c r="R59" t="n">
-        <v>6781931</v>
+        <v>6781936</v>
       </c>
       <c r="S59" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7274,12 +7314,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7294,74 +7344,69 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119169048</t>
+          <t>https://artportalen.se/Sighting/136556999</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119039990</v>
+        <v>136557001</v>
       </c>
       <c r="B60" t="n">
-        <v>8455</v>
+        <v>93400</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Unänget, Dlr</t>
+          <t>Tallås N Hedens återvinningscentral, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>481947</v>
+        <v>481922</v>
       </c>
       <c r="R60" t="n">
-        <v>6781935</v>
+        <v>6781947</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7385,12 +7430,27 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Gammal fkr</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7399,81 +7459,80 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119039990</t>
+          <t>https://artportalen.se/Sighting/136557001</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119169051</v>
+        <v>136557011</v>
       </c>
       <c r="B61" t="n">
-        <v>8455</v>
+        <v>93400</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Heden, Dlr</t>
+          <t>Tallås N Hedens återvinningscentral, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>481942</v>
+        <v>481940</v>
       </c>
       <c r="R61" t="n">
-        <v>6781931</v>
+        <v>6782027</v>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7497,12 +7556,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7511,34 +7580,33 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119169051</t>
+          <t>https://artportalen.se/Sighting/136557011</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119168995</v>
+        <v>119382427</v>
       </c>
       <c r="B62" t="n">
-        <v>99781</v>
+        <v>90522</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7546,41 +7614,40 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222309</v>
+        <v>4962</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Heden, Dlr</t>
+          <t>Heden, Heden, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>481914</v>
+        <v>481946</v>
       </c>
       <c r="R62" t="n">
-        <v>6781934</v>
+        <v>6781952</v>
       </c>
       <c r="S62" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7604,12 +7671,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7630,22 +7707,22 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119168995</t>
+          <t>https://artportalen.se/Sighting/119382427</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119168998</v>
+        <v>104286582</v>
       </c>
       <c r="B63" t="n">
-        <v>99781</v>
+        <v>93235</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7653,41 +7730,48 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222309</v>
+        <v>5966</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Heden, Dlr</t>
+          <t>N Heden, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>481913</v>
+        <v>481927</v>
       </c>
       <c r="R63" t="n">
-        <v>6781940</v>
+        <v>6781938</v>
       </c>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7711,12 +7795,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2022-10-23</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2022-10-23</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7732,27 +7816,27 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119168998</t>
+          <t>https://artportalen.se/Sighting/104286582</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119169013</v>
+        <v>128505843</v>
       </c>
       <c r="B64" t="n">
-        <v>99781</v>
+        <v>93235</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7760,41 +7844,46 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222309</v>
+        <v>5966</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Heden, Dlr</t>
+          <t>Heden, Heden, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>481920</v>
+        <v>481924</v>
       </c>
       <c r="R64" t="n">
-        <v>6781960</v>
+        <v>6781967</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7818,12 +7907,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7832,7 +7931,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7844,22 +7942,22 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119169013</t>
+          <t>https://artportalen.se/Sighting/128505843</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119169019</v>
+        <v>128505857</v>
       </c>
       <c r="B65" t="n">
-        <v>99781</v>
+        <v>93235</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7867,41 +7965,46 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222309</v>
+        <v>5966</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Heden, Dlr</t>
+          <t>Heden, Heden, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>481920</v>
+        <v>481928</v>
       </c>
       <c r="R65" t="n">
-        <v>6781968</v>
+        <v>6781979</v>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7925,12 +8028,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7939,7 +8052,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7951,22 +8063,22 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119169019</t>
+          <t>https://artportalen.se/Sighting/128505857</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119168889</v>
+        <v>128712673</v>
       </c>
       <c r="B66" t="n">
-        <v>91402</v>
+        <v>93235</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7974,37 +8086,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>256703</v>
+        <v>5966</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Heden, Dlr</t>
+          <t>Heden, Heden, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>481930</v>
+        <v>481932</v>
       </c>
       <c r="R66" t="n">
-        <v>6782015</v>
+        <v>6781901</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8031,12 +8140,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8045,7 +8164,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -8057,22 +8175,22 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119168889</t>
+          <t>https://artportalen.se/Sighting/128712673</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128619237</v>
+        <v>128712893</v>
       </c>
       <c r="B67" t="n">
-        <v>91402</v>
+        <v>93235</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8080,21 +8198,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>256703</v>
+        <v>5966</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8104,13 +8222,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>481932</v>
+        <v>481950</v>
       </c>
       <c r="R67" t="n">
-        <v>6782005</v>
+        <v>6782002</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8134,22 +8252,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8175,54 +8293,63 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128619237</t>
+          <t>https://artportalen.se/Sighting/128712893</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>136024097</v>
+        <v>125153302</v>
       </c>
       <c r="B68" t="n">
-        <v>91580</v>
+        <v>79327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>256703</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Tallås N Hedens återvinningscentral, Dlr</t>
+          <t>Unänget, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>481964</v>
+        <v>481960</v>
       </c>
       <c r="R68" t="n">
-        <v>6782031</v>
+        <v>6782003</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8246,22 +8373,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8276,16 +8403,1331 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125153302</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>119039963</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Unänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>481902</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6781960</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119039963</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>119169048</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Heden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>481942</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6781931</v>
+      </c>
+      <c r="S70" t="n">
+        <v>1</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119169048</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>119039990</v>
+      </c>
+      <c r="B71" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Unänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>481947</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6781935</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119039990</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>119169051</v>
+      </c>
+      <c r="B72" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Heden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>481942</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6781931</v>
+      </c>
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119169051</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>136556991</v>
+      </c>
+      <c r="B73" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Tallås N Hedens återvinningscentral, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>481988</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6782042</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136556991</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>119168995</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Heden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>481914</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6781934</v>
+      </c>
+      <c r="S74" t="n">
+        <v>1</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119168995</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>119168998</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Heden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>481913</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6781940</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119168998</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>119169013</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Heden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>481920</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6781960</v>
+      </c>
+      <c r="S76" t="n">
+        <v>1</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119169013</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>119169019</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Heden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>481920</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6781968</v>
+      </c>
+      <c r="S77" t="n">
+        <v>1</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119169019</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>119168889</v>
+      </c>
+      <c r="B78" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Heden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>481930</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6782015</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119168889</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>128619237</v>
+      </c>
+      <c r="B79" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Hed, Hed, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>481932</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6782005</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128619237</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>136024097</v>
+      </c>
+      <c r="B80" t="n">
+        <v>91581</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Tallås N Hedens återvinningscentral, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>481964</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6782031</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136024097</t>
         </is>
@@ -8360,6 +9802,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
